--- a/public/template/机组花名册.xlsx
+++ b/public/template/机组花名册.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="377">
   <si>
     <t>员工号</t>
   </si>
@@ -35,15 +35,24 @@
     <t>姓名</t>
   </si>
   <si>
+    <t>技术信息</t>
+  </si>
+  <si>
     <t>伍文彬</t>
   </si>
   <si>
+    <t>777:飞行教员C</t>
+  </si>
+  <si>
     <t>李星龙</t>
   </si>
   <si>
     <t>夏晴</t>
   </si>
   <si>
+    <t>777:飞行教员B</t>
+  </si>
+  <si>
     <t>姚诚</t>
   </si>
   <si>
@@ -83,9 +92,6 @@
     <t>刘小伟</t>
   </si>
   <si>
-    <t>李映宏</t>
-  </si>
-  <si>
     <t>肖一</t>
   </si>
   <si>
@@ -179,9 +185,18 @@
     <t>寇西武</t>
   </si>
   <si>
+    <t>王锐</t>
+  </si>
+  <si>
+    <t>孔繁平</t>
+  </si>
+  <si>
     <t>石桂平</t>
   </si>
   <si>
+    <t>777:飞行教员A</t>
+  </si>
+  <si>
     <t>向宇宽</t>
   </si>
   <si>
@@ -239,9 +254,6 @@
     <t>唐兴旺</t>
   </si>
   <si>
-    <t>王锐</t>
-  </si>
-  <si>
     <t>马堃锭</t>
   </si>
   <si>
@@ -266,9 +278,6 @@
     <t>张吉</t>
   </si>
   <si>
-    <t>闫珺熠</t>
-  </si>
-  <si>
     <t>张佳霖</t>
   </si>
   <si>
@@ -287,18 +296,12 @@
     <t>冀文龙</t>
   </si>
   <si>
-    <t>张勇</t>
-  </si>
-  <si>
     <t>陈志鹏</t>
   </si>
   <si>
     <t>刘作炫</t>
   </si>
   <si>
-    <t>薛杨</t>
-  </si>
-  <si>
     <t>罗建勇</t>
   </si>
   <si>
@@ -320,15 +323,24 @@
     <t>汤光磊</t>
   </si>
   <si>
+    <t>孙玉虎</t>
+  </si>
+  <si>
+    <t>方建斌</t>
+  </si>
+  <si>
+    <t>张琪</t>
+  </si>
+  <si>
     <t>Jochen Etienne L DE WISPELAERE</t>
   </si>
   <si>
+    <t>777:D类机长</t>
+  </si>
+  <si>
     <t>Jan HRASKO</t>
   </si>
   <si>
-    <t>孙玉虎</t>
-  </si>
-  <si>
     <t>刘源</t>
   </si>
   <si>
@@ -338,9 +350,6 @@
     <t>许宁</t>
   </si>
   <si>
-    <t>方建斌</t>
-  </si>
-  <si>
     <t>梁浩</t>
   </si>
   <si>
@@ -353,24 +362,21 @@
     <t>陶炼</t>
   </si>
   <si>
+    <t>777:C类机长</t>
+  </si>
+  <si>
     <t>李春平</t>
   </si>
   <si>
     <t>沈欣</t>
   </si>
   <si>
-    <t>朱嘉俊</t>
-  </si>
-  <si>
     <t>孙世峰</t>
   </si>
   <si>
     <t>彭程</t>
   </si>
   <si>
-    <t>冯志权</t>
-  </si>
-  <si>
     <t>李旭波</t>
   </si>
   <si>
@@ -380,18 +386,12 @@
     <t>张长伟</t>
   </si>
   <si>
-    <t>蒋学隆</t>
-  </si>
-  <si>
     <t>叶锐章</t>
   </si>
   <si>
     <t>张冀</t>
   </si>
   <si>
-    <t>龚智龙</t>
-  </si>
-  <si>
     <t>王彤阳</t>
   </si>
   <si>
@@ -413,9 +413,6 @@
     <t>张祺</t>
   </si>
   <si>
-    <t>刘超群</t>
-  </si>
-  <si>
     <t>连彦辉</t>
   </si>
   <si>
@@ -425,30 +422,15 @@
     <t>王阳</t>
   </si>
   <si>
-    <t>张琪</t>
-  </si>
-  <si>
-    <t>罗竣艺</t>
-  </si>
-  <si>
     <t>蒋文斌</t>
   </si>
   <si>
-    <t>王佳楠</t>
-  </si>
-  <si>
     <t>尤晓</t>
   </si>
   <si>
     <t>王琦</t>
   </si>
   <si>
-    <t>高思宇</t>
-  </si>
-  <si>
-    <t>张雨</t>
-  </si>
-  <si>
     <t>胡佳欣</t>
   </si>
   <si>
@@ -518,24 +500,27 @@
     <t>萧瑞胜</t>
   </si>
   <si>
+    <t>冯涛</t>
+  </si>
+  <si>
+    <t>朱磊</t>
+  </si>
+  <si>
+    <t>莫文龙</t>
+  </si>
+  <si>
+    <t>李灿</t>
+  </si>
+  <si>
     <t>赵子超</t>
   </si>
   <si>
-    <t>朱磊</t>
-  </si>
-  <si>
-    <t>冯涛</t>
-  </si>
-  <si>
-    <t>莫文龙</t>
+    <t>777:B类机长</t>
   </si>
   <si>
     <t>王靖江</t>
   </si>
   <si>
-    <t>李灿</t>
-  </si>
-  <si>
     <t>余俊</t>
   </si>
   <si>
@@ -569,30 +554,30 @@
     <t>钱少龙</t>
   </si>
   <si>
+    <t>张竞怡</t>
+  </si>
+  <si>
+    <t>郭春阳</t>
+  </si>
+  <si>
+    <t>张寒义</t>
+  </si>
+  <si>
+    <t>唐浩林</t>
+  </si>
+  <si>
     <t>韩龙</t>
   </si>
   <si>
-    <t>张竞怡</t>
+    <t>777:Z类机长</t>
   </si>
   <si>
     <t>盛况</t>
   </si>
   <si>
-    <t>张寒义</t>
-  </si>
-  <si>
     <t>崔玉柱</t>
   </si>
   <si>
-    <t>李晓波</t>
-  </si>
-  <si>
-    <t>郭春阳</t>
-  </si>
-  <si>
-    <t>唐浩林</t>
-  </si>
-  <si>
     <t>周思宁</t>
   </si>
   <si>
@@ -644,30 +629,24 @@
     <t>赵亚伟</t>
   </si>
   <si>
+    <t>777:E类副驾驶</t>
+  </si>
+  <si>
     <t>吴润雨</t>
   </si>
   <si>
+    <t>777:D类副驾驶</t>
+  </si>
+  <si>
     <t>全棣伟</t>
   </si>
   <si>
-    <t>李晋诣</t>
-  </si>
-  <si>
-    <t>陈利勤</t>
-  </si>
-  <si>
     <t>李泰成</t>
   </si>
   <si>
     <t>余希</t>
   </si>
   <si>
-    <t>周永富</t>
-  </si>
-  <si>
-    <t>李鹏</t>
-  </si>
-  <si>
     <t>王若飞</t>
   </si>
   <si>
@@ -683,6 +662,9 @@
     <t>谢旭纬</t>
   </si>
   <si>
+    <t>777:C类副驾驶</t>
+  </si>
+  <si>
     <t>沙思丞</t>
   </si>
   <si>
@@ -746,9 +728,30 @@
     <t>王晨旭</t>
   </si>
   <si>
+    <t>曾渝浩</t>
+  </si>
+  <si>
+    <t>尹培玉</t>
+  </si>
+  <si>
+    <t>汪润泽</t>
+  </si>
+  <si>
+    <t>李天诚</t>
+  </si>
+  <si>
+    <t>张怡君</t>
+  </si>
+  <si>
+    <t>陈振浩</t>
+  </si>
+  <si>
     <t>陈兆铭</t>
   </si>
   <si>
+    <t>777:B类副驾驶</t>
+  </si>
+  <si>
     <t>周锐豪</t>
   </si>
   <si>
@@ -767,24 +770,15 @@
     <t>张子硕</t>
   </si>
   <si>
-    <t>张怡君</t>
-  </si>
-  <si>
     <t>苏逸海</t>
   </si>
   <si>
-    <t>陈振浩</t>
-  </si>
-  <si>
     <t>岑健勇</t>
   </si>
   <si>
     <t>陈祥琛</t>
   </si>
   <si>
-    <t>李天诚</t>
-  </si>
-  <si>
     <t>周诗健</t>
   </si>
   <si>
@@ -812,9 +806,6 @@
     <t>姜泽</t>
   </si>
   <si>
-    <t>汪润泽</t>
-  </si>
-  <si>
     <t>卢勇成</t>
   </si>
   <si>
@@ -830,12 +821,6 @@
     <t>刘育辰</t>
   </si>
   <si>
-    <t>曾渝浩</t>
-  </si>
-  <si>
-    <t>尹培玉</t>
-  </si>
-  <si>
     <t>黄磊</t>
   </si>
   <si>
@@ -866,12 +851,33 @@
     <t>李振洋</t>
   </si>
   <si>
+    <t>曹宏博</t>
+  </si>
+  <si>
+    <t>付杰明</t>
+  </si>
+  <si>
+    <t>唐健翔</t>
+  </si>
+  <si>
+    <t>赵宇航</t>
+  </si>
+  <si>
     <t>沈铭</t>
   </si>
   <si>
+    <t>周桐</t>
+  </si>
+  <si>
+    <t>税毅</t>
+  </si>
+  <si>
     <t>杨帮翔</t>
   </si>
   <si>
+    <t>777:A2类副驾驶</t>
+  </si>
+  <si>
     <t>刘镇毓</t>
   </si>
   <si>
@@ -890,9 +896,6 @@
     <t>胡轩铭</t>
   </si>
   <si>
-    <t>周桐</t>
-  </si>
-  <si>
     <t>陈子其</t>
   </si>
   <si>
@@ -917,18 +920,9 @@
     <t>杨登科</t>
   </si>
   <si>
-    <t>税毅</t>
-  </si>
-  <si>
     <t>陈致远</t>
   </si>
   <si>
-    <t>唐健翔</t>
-  </si>
-  <si>
-    <t>付杰明</t>
-  </si>
-  <si>
     <t>何鹏程</t>
   </si>
   <si>
@@ -944,12 +938,6 @@
     <t>陈昭旻</t>
   </si>
   <si>
-    <t>曹宏博</t>
-  </si>
-  <si>
-    <t>赵宇航</t>
-  </si>
-  <si>
     <t>黄家和</t>
   </si>
   <si>
@@ -1022,12 +1010,30 @@
     <t>王年鹏</t>
   </si>
   <si>
+    <t>戴永康</t>
+  </si>
+  <si>
     <t>刘千里</t>
   </si>
   <si>
+    <t>张靖博</t>
+  </si>
+  <si>
+    <t>蒙炳志</t>
+  </si>
+  <si>
+    <t>路舜锋</t>
+  </si>
+  <si>
+    <t>许哲华</t>
+  </si>
+  <si>
     <t>庞凌博</t>
   </si>
   <si>
+    <t>777:A1类副驾驶</t>
+  </si>
+  <si>
     <t>闫文平</t>
   </si>
   <si>
@@ -1037,21 +1043,9 @@
     <t>王熠铭</t>
   </si>
   <si>
-    <t>戴永康</t>
-  </si>
-  <si>
-    <t>路舜锋</t>
-  </si>
-  <si>
-    <t>张靖博</t>
-  </si>
-  <si>
     <t>黄捷</t>
   </si>
   <si>
-    <t>蒙炳志</t>
-  </si>
-  <si>
     <t>李嘉杰</t>
   </si>
   <si>
@@ -1070,9 +1064,6 @@
     <t>文强</t>
   </si>
   <si>
-    <t>许哲华</t>
-  </si>
-  <si>
     <t>黄兴</t>
   </si>
   <si>
@@ -1121,6 +1112,9 @@
     <t>朱慕杰</t>
   </si>
   <si>
+    <t>罗浩诚</t>
+  </si>
+  <si>
     <t>吴智鑫</t>
   </si>
   <si>
@@ -1139,13 +1133,31 @@
     <t>孙金晨</t>
   </si>
   <si>
-    <t>罗浩诚</t>
-  </si>
-  <si>
     <t>刘宇</t>
   </si>
   <si>
-    <t>孔繁平</t>
+    <t>吕博文</t>
+  </si>
+  <si>
+    <t>划转副驾驶</t>
+  </si>
+  <si>
+    <t>温佳明</t>
+  </si>
+  <si>
+    <t>钱坤洋</t>
+  </si>
+  <si>
+    <t>包忠杰</t>
+  </si>
+  <si>
+    <t>贾生琨</t>
+  </si>
+  <si>
+    <t>周艺阳</t>
+  </si>
+  <si>
+    <t>杨宇轩</t>
   </si>
 </sst>
 </file>
@@ -1799,7 +1811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1823,6 +1835,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2356,2990 +2371,4041 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B372"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:C1048576"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="15.6272727272727" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="3">
         <v>181781</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="3">
         <v>181834</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="4">
         <v>186605</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="3">
         <v>901735</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="3">
         <v>196003</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" s="3">
         <v>201141</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3">
       <c r="A8" s="3">
         <v>206534</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="3">
         <v>901478</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>12</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10" s="3">
         <v>209224</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>13</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" s="3">
         <v>901692</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>14</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" s="3">
         <v>181643</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="3">
         <v>197646</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="3">
         <v>181524</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="3">
         <v>188411</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="3">
         <v>901468</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>19</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="3">
         <v>191473</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>20</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="3">
-        <v>181761</v>
+        <v>196325</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>21</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="3">
-        <v>196325</v>
+        <v>198174</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>22</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="3">
-        <v>198174</v>
+        <v>204943</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>23</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="3">
-        <v>204943</v>
+        <v>198193</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>24</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="3">
-        <v>198193</v>
+        <v>901697</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>25</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="3">
-        <v>901697</v>
+        <v>901729</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>26</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="3">
-        <v>901729</v>
+        <v>209081</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>27</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
       <c r="A25" s="3">
-        <v>209081</v>
+        <v>198254</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="3">
-        <v>198254</v>
+        <v>28</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="4">
+        <v>183014</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>29</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="4">
-        <v>183014</v>
+        <v>181681</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="4">
-        <v>181681</v>
+        <v>30</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3">
+        <v>198287</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>31</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="3">
-        <v>198287</v>
+        <v>209232</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>32</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="3">
-        <v>209232</v>
+        <v>206757</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>33</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="A31" s="3">
-        <v>206757</v>
+        <v>206949</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>34</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="A32" s="3">
-        <v>206949</v>
+        <v>193182</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>35</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33" s="3">
-        <v>193182</v>
+        <v>186640</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>36</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34" s="3">
-        <v>186640</v>
+        <v>181773</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>37</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35" s="3">
-        <v>181773</v>
+        <v>181578</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>38</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36" s="3">
-        <v>181578</v>
+        <v>199691</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>39</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37" s="3">
-        <v>199691</v>
+        <v>210518</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>40</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
       <c r="A38" s="3">
-        <v>210518</v>
+        <v>181831</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="3">
-        <v>181831</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>41</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="5">
+        <v>181806</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40" s="5">
-        <v>181806</v>
+        <v>181848</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="5">
-        <v>181848</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>43</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="6">
+        <v>901593</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="A42" s="6">
-        <v>901593</v>
+        <v>901648</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="6">
-        <v>901648</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>45</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="3">
+        <v>181762</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="A44" s="3">
-        <v>181762</v>
+        <v>203105</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="3">
-        <v>203105</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="6">
+        <v>47</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="6">
         <v>193213</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+      <c r="B45" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="3">
+        <v>196267</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="3">
-        <v>196267</v>
+        <v>210541</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="3">
-        <v>210541</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="6">
+        <v>50</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="6">
         <v>181764</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="3">
+      <c r="B48" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="3">
+        <v>901658</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="6">
+        <v>706596</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="3">
         <v>191452</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="3">
+      <c r="B51" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="3">
         <v>208985</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="3">
+      <c r="B52" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="3">
         <v>206632</v>
       </c>
-      <c r="B52" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="3">
+      <c r="B53" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="3">
         <v>199680</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="3">
+      <c r="B54" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="3">
         <v>181503</v>
       </c>
-      <c r="B54" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="3">
+      <c r="B55" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="3">
         <v>181513</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B56" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="3">
+    <row r="57" spans="1:3">
+      <c r="A57" s="3">
         <v>181558</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="3">
+      <c r="B57" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="3">
         <v>181727</v>
       </c>
-      <c r="B57" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="3">
+      <c r="B58" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="3">
         <v>186662</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="3">
+      <c r="B59" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="3">
         <v>193391</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="3">
+      <c r="B60" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="3">
         <v>201906</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="3">
+      <c r="B61" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="3">
         <v>202990</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="3">
+      <c r="B62" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="3">
         <v>901768</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="3">
+      <c r="B63" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="3">
         <v>201982</v>
       </c>
-      <c r="B63" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="3">
+      <c r="B64" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="3">
         <v>210535</v>
       </c>
-      <c r="B64" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="3">
+      <c r="B65" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="3">
         <v>905175</v>
       </c>
-      <c r="B65" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="3">
+      <c r="B66" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="3">
         <v>901449</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="3">
+      <c r="B67" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="3">
         <v>181798</v>
       </c>
-      <c r="B67" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="3">
+      <c r="B68" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="3">
         <v>187952</v>
       </c>
-      <c r="B68" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="3">
+      <c r="B69" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="3">
         <v>196520</v>
       </c>
-      <c r="B69" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="3">
-        <v>901658</v>
-      </c>
       <c r="B70" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>74</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" s="3">
         <v>213485</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>75</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="3">
         <v>212801</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>76</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" s="3">
         <v>189182</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>77</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74" s="3">
         <v>181783</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>78</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" s="6">
         <v>198207</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>79</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" s="6">
         <v>204821</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>80</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" s="3">
         <v>216861</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>81</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" s="3">
         <v>210252</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>82</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" s="3">
-        <v>216502</v>
+        <v>214335</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" s="3">
-        <v>214335</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>83</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="5">
+        <v>202368</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" s="5">
-        <v>202368</v>
+        <v>211430</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" s="5">
-        <v>211430</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>85</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="3">
+        <v>215055</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" s="3">
-        <v>215055</v>
+        <v>186643</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>87</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84" s="3">
-        <v>186643</v>
+        <v>206748</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" s="3">
-        <v>206748</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" s="3">
-        <v>181851</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>88</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="6">
+        <v>183002</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="6">
+        <v>207285</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87" s="6">
-        <v>183002</v>
+        <v>202417</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>91</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88" s="6">
-        <v>207285</v>
+        <v>208732</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="4">
-        <v>901714</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>92</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="6">
+        <v>198204</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90" s="6">
-        <v>202417</v>
+        <v>207623</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>94</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" s="6">
-        <v>208732</v>
+        <v>213174</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>95</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92" s="6">
-        <v>198204</v>
+        <v>901785</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>96</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93" s="6">
-        <v>207623</v>
+        <v>181688</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="6">
-        <v>213174</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
+        <v>97</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="5">
+        <v>901621</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95" s="6">
-        <v>901785</v>
+        <v>186663</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="6">
-        <v>181688</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="97" ht="42" spans="1:2">
+        <v>99</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="3">
+        <v>207621</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="97" ht="42" spans="1:3">
       <c r="A97" s="6">
         <v>777575</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>101</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" s="6">
         <v>771602</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" s="5">
-        <v>901621</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="3">
+        <v>103</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="3">
         <v>215610</v>
       </c>
-      <c r="B100" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="6">
+      <c r="B99" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="6">
         <v>213091</v>
       </c>
-      <c r="B101" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" s="3">
+      <c r="B100" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="3">
         <v>213107</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B101" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C101" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
-      <c r="A103" s="6">
-        <v>186663</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="6">
+    <row r="102" spans="1:3">
+      <c r="A102" s="6">
         <v>901531</v>
       </c>
-      <c r="B104" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
+      <c r="B102" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="3">
+        <v>216505</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="3">
+        <v>210899</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
       <c r="A105" s="3">
-        <v>216505</v>
+        <v>210510</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
+        <v>110</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
       <c r="A106" s="3">
-        <v>210899</v>
+        <v>193177</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
+        <v>112</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107" s="3">
-        <v>210510</v>
+        <v>202989</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
+        <v>113</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
       <c r="A108" s="3">
-        <v>193177</v>
+        <v>208984</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
+        <v>114</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
       <c r="A109" s="3">
-        <v>202989</v>
+        <v>212810</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
+        <v>115</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
       <c r="A110" s="3">
-        <v>208978</v>
+        <v>193238</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
+        <v>116</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
       <c r="A111" s="3">
-        <v>208984</v>
+        <v>212914</v>
       </c>
       <c r="B111" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C111" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:3">
       <c r="A112" s="3">
-        <v>212810</v>
+        <v>196015</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
+        <v>118</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
       <c r="A113" s="3">
-        <v>184767</v>
+        <v>206751</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
+        <v>119</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
       <c r="A114" s="3">
-        <v>193238</v>
+        <v>193002</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
+        <v>120</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
       <c r="A115" s="3">
-        <v>212914</v>
+        <v>212934</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
+        <v>121</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
       <c r="A116" s="3">
-        <v>196015</v>
+        <v>196557</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
+        <v>122</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
       <c r="A117" s="3">
-        <v>216757</v>
+        <v>211303</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
+        <v>123</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
       <c r="A118" s="3">
-        <v>206751</v>
+        <v>212946</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
+        <v>124</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
       <c r="A119" s="3">
-        <v>193002</v>
+        <v>708722</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
+        <v>125</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
       <c r="A120" s="3">
-        <v>209990</v>
+        <v>210782</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
+        <v>126</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
       <c r="A121" s="3">
-        <v>212934</v>
+        <v>210123</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
+        <v>127</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
       <c r="A122" s="3">
-        <v>196557</v>
+        <v>202057</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
+        <v>128</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
       <c r="A123" s="3">
-        <v>211303</v>
+        <v>211509</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
+        <v>129</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
       <c r="A124" s="3">
-        <v>212946</v>
+        <v>207632</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
+        <v>130</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
       <c r="A125" s="3">
-        <v>708722</v>
+        <v>189969</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="3">
-        <v>210782</v>
-      </c>
-      <c r="B126" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="3">
-        <v>210123</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="3">
-        <v>211566</v>
+        <v>131</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="5">
+        <v>211542</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="5">
+        <v>612061</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="4">
+        <v>224079</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
+        <v>134</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
       <c r="A129" s="3">
-        <v>202057</v>
+        <v>218326</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="3">
-        <v>211509</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="3">
-        <v>207632</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
+        <v>135</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="6">
+        <v>611893</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="131" ht="42" spans="1:3">
+      <c r="A131" s="6">
+        <v>263574</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
       <c r="A132" s="3">
-        <v>207621</v>
+        <v>210227</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="3">
-        <v>210239</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="3">
-        <v>189969</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
+        <v>138</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="6">
+        <v>181594</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="6">
+        <v>196312</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
       <c r="A135" s="4">
-        <v>216750</v>
+        <v>211590</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="5">
-        <v>211542</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="5">
-        <v>612061</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="4">
-        <v>215060</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="4">
-        <v>215056</v>
+        <v>141</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="3">
+        <v>192425</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="4">
+        <v>212660</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="6">
+        <v>201138</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="3">
+        <v>212871</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
+        <v>145</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
       <c r="A140" s="4">
-        <v>224079</v>
+        <v>206950</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
+        <v>146</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
       <c r="A141" s="3">
-        <v>218326</v>
+        <v>209259</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
+        <v>147</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="142" ht="28" spans="1:3">
       <c r="A142" s="6">
-        <v>611893</v>
+        <v>248809</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="143" ht="42" spans="1:2">
+        <v>148</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
       <c r="A143" s="6">
-        <v>263574</v>
+        <v>213078</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="3">
-        <v>210227</v>
+        <v>149</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="4">
+        <v>217555</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="6">
-        <v>181594</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="6">
-        <v>196312</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="4">
-        <v>211590</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
+        <v>150</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="4">
+        <v>206324</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="3">
+        <v>217117</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="6">
+        <v>901500</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
       <c r="A148" s="3">
-        <v>192425</v>
+        <v>195814</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="4">
-        <v>212660</v>
+        <v>154</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="3">
+        <v>225674</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="6">
-        <v>201138</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
+        <v>155</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" s="3">
+        <v>186664</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
       <c r="A151" s="3">
-        <v>212871</v>
+        <v>234426</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="4">
-        <v>206950</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="3">
-        <v>209259</v>
+        <v>157</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" s="6">
+        <v>209178</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="4">
+        <v>211558</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="154" ht="28" spans="1:2">
-      <c r="A154" s="6">
-        <v>248809</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="6">
-        <v>213078</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
+        <v>159</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="3">
+        <v>217695</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="3">
+        <v>188592</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
       <c r="A156" s="4">
-        <v>217555</v>
+        <v>211937</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="4">
-        <v>206324</v>
+        <v>163</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" s="3">
+        <v>208107</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="3">
-        <v>217117</v>
+        <v>164</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="4">
+        <v>210767</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="6">
-        <v>901500</v>
-      </c>
-      <c r="B159" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
+        <v>165</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="3">
+        <v>903942</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
       <c r="A160" s="3">
-        <v>195814</v>
+        <v>189186</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
+        <v>167</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
       <c r="A161" s="3">
-        <v>225674</v>
+        <v>905161</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="3">
-        <v>186664</v>
-      </c>
-      <c r="B162" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="162" spans="1:3">
+      <c r="A162" s="6">
+        <v>192993</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
       <c r="A163" s="3">
-        <v>188592</v>
+        <v>210155</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="6">
-        <v>209178</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
+        <v>170</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="3">
+        <v>901756</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
       <c r="A165" s="3">
-        <v>234426</v>
+        <v>901557</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="4">
-        <v>211558</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
+        <v>172</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="6">
+        <v>904950</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
       <c r="A167" s="4">
-        <v>211937</v>
+        <v>210625</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
+        <v>174</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
       <c r="A168" s="3">
-        <v>217695</v>
+        <v>215073</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="3">
-        <v>208107</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="4">
-        <v>210767</v>
+        <v>175</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="5">
+        <v>184790</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="3">
+        <v>219807</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="3">
-        <v>903942</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
+        <v>177</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" s="6">
+        <v>211588</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
       <c r="A172" s="3">
-        <v>189186</v>
+        <v>214908</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
+        <v>179</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
       <c r="A173" s="3">
-        <v>905161</v>
+        <v>211318</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="6">
-        <v>192993</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="3">
-        <v>210155</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="3">
-        <v>901756</v>
-      </c>
-      <c r="B176" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="3">
-        <v>901557</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
+        <v>181</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" s="3">
+        <v>210787</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" s="6">
+        <v>210135</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" s="6">
+        <v>210264</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" s="6">
+        <v>218359</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
       <c r="A178" s="6">
-        <v>904950</v>
+        <v>211594</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="4">
-        <v>210625</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="3">
-        <v>214908</v>
-      </c>
-      <c r="B180" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C178" s="4" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="3">
-        <v>215073</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="3">
-        <v>211318</v>
-      </c>
-      <c r="B182" s="4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="3">
-        <v>219807</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="3">
-        <v>210787</v>
-      </c>
-      <c r="B184" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="3">
-        <v>205130</v>
-      </c>
-      <c r="B185" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="5">
-        <v>184790</v>
-      </c>
-      <c r="B186" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
+    <row r="179" spans="1:3">
+      <c r="A179" s="6">
+        <v>224562</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" s="6">
+        <v>212815</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" s="6">
+        <v>189900</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="6">
+        <v>217164</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" s="6">
+        <v>212657</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" s="6">
+        <v>213366</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" s="6">
+        <v>211575</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" s="6">
+        <v>211407</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3">
       <c r="A187" s="6">
-        <v>211588</v>
+        <v>211410</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
+        <v>195</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3">
       <c r="A188" s="6">
-        <v>210135</v>
+        <v>211264</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
+        <v>196</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3">
       <c r="A189" s="6">
-        <v>210264</v>
+        <v>182998</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
+        <v>197</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3">
       <c r="A190" s="6">
-        <v>218359</v>
+        <v>217707</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="6">
-        <v>211594</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="6">
-        <v>224562</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="6">
-        <v>212815</v>
-      </c>
-      <c r="B193" s="7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="6">
-        <v>189900</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="6">
-        <v>217164</v>
-      </c>
-      <c r="B195" s="7" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="6">
-        <v>212657</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2">
-      <c r="A197" s="6">
-        <v>213366</v>
-      </c>
-      <c r="B197" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="A198" s="6">
-        <v>211575</v>
-      </c>
-      <c r="B198" s="7" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="199" spans="1:2">
-      <c r="A199" s="6">
-        <v>211407</v>
-      </c>
-      <c r="B199" s="7" t="s">
+      <c r="C190" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" s="3">
+        <v>202379</v>
+      </c>
+      <c r="B191" s="4" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="A200" s="6">
-        <v>211410</v>
-      </c>
-      <c r="B200" s="7" t="s">
+      <c r="C191" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
-      <c r="A201" s="6">
-        <v>211264</v>
-      </c>
-      <c r="B201" s="7" t="s">
+    <row r="192" spans="1:3">
+      <c r="A192" s="3">
+        <v>240677</v>
+      </c>
+      <c r="B192" s="4" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="202" spans="1:2">
-      <c r="A202" s="6">
-        <v>182998</v>
-      </c>
-      <c r="B202" s="7" t="s">
+      <c r="C192" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
-      <c r="A203" s="6">
-        <v>217707</v>
-      </c>
-      <c r="B203" s="7" t="s">
+    <row r="193" spans="1:3">
+      <c r="A193" s="3">
+        <v>259806</v>
+      </c>
+      <c r="B193" s="4" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="204" spans="1:2">
+      <c r="C193" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" s="3">
+        <v>236217</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" s="3">
+        <v>248907</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" s="3">
+        <v>260944</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" s="3">
+        <v>257606</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" s="3">
+        <v>251924</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" s="3">
+        <v>273299</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" s="3">
+        <v>230397</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" s="3">
+        <v>248322</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" s="3">
+        <v>248319</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" s="3">
+        <v>258463</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
       <c r="A204" s="3">
-        <v>202379</v>
+        <v>261764</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2">
+        <v>215</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
       <c r="A205" s="3">
-        <v>240677</v>
+        <v>262062</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2">
+        <v>216</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
       <c r="A206" s="3">
-        <v>259806</v>
+        <v>265806</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2">
+        <v>217</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
       <c r="A207" s="3">
-        <v>248310</v>
+        <v>265801</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2">
-      <c r="A208" s="3">
-        <v>248320</v>
-      </c>
-      <c r="B208" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2">
+        <v>218</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" s="6">
+        <v>210590</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3">
       <c r="A209" s="3">
-        <v>236217</v>
+        <v>257603</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2">
+        <v>220</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3">
       <c r="A210" s="3">
-        <v>248907</v>
+        <v>253772</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2">
+        <v>221</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3">
       <c r="A211" s="3">
-        <v>251920</v>
+        <v>259803</v>
       </c>
       <c r="B211" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C211" s="4" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
+    <row r="212" spans="1:3">
       <c r="A212" s="3">
-        <v>247692</v>
+        <v>263416</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2">
+        <v>223</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3">
       <c r="A213" s="3">
-        <v>260944</v>
+        <v>247704</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2">
-      <c r="A214" s="3">
-        <v>257606</v>
-      </c>
-      <c r="B214" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2">
+        <v>224</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" s="5">
+        <v>212982</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3">
       <c r="A215" s="3">
-        <v>251924</v>
+        <v>271938</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
+        <v>226</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3">
       <c r="A216" s="3">
-        <v>273299</v>
+        <v>282153</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2">
-      <c r="A217" s="3">
-        <v>230397</v>
-      </c>
-      <c r="B217" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2">
+        <v>227</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217" s="6">
+        <v>257697</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3">
       <c r="A218" s="3">
-        <v>248322</v>
+        <v>265822</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2">
+        <v>229</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3">
       <c r="A219" s="3">
-        <v>248319</v>
+        <v>266499</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
+        <v>230</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3">
       <c r="A220" s="3">
-        <v>258463</v>
+        <v>253776</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2">
+        <v>231</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
       <c r="A221" s="3">
-        <v>261764</v>
+        <v>270795</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2">
-      <c r="A222" s="3">
-        <v>262062</v>
-      </c>
-      <c r="B222" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2">
-      <c r="A223" s="3">
-        <v>265806</v>
+        <v>232</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222" s="5">
+        <v>276035</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223" s="4">
+        <v>285839</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2">
-      <c r="A224" s="3">
-        <v>265801</v>
+        <v>234</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" s="4">
+        <v>278078</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2">
-      <c r="A225" s="6">
-        <v>210590</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2">
-      <c r="A226" s="3">
-        <v>257603</v>
+        <v>235</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225" s="3">
+        <v>264179</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" s="4">
+        <v>281972</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2">
+        <v>237</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
       <c r="A227" s="3">
-        <v>253772</v>
+        <v>276707</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2">
+        <v>238</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
       <c r="A228" s="3">
-        <v>259803</v>
+        <v>270784</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2">
+        <v>239</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
       <c r="A229" s="3">
-        <v>263416</v>
+        <v>271943</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2">
+        <v>241</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
       <c r="A230" s="3">
-        <v>247704</v>
+        <v>247695</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2">
-      <c r="A231" s="5">
-        <v>212982</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2">
+        <v>242</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" s="3">
+        <v>253781</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
       <c r="A232" s="3">
-        <v>271938</v>
+        <v>211631</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2">
-      <c r="A233" s="3">
-        <v>282153</v>
-      </c>
-      <c r="B233" s="4" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="234" spans="1:2">
-      <c r="A234" s="6">
-        <v>257697</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2">
+        <v>244</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" s="6">
+        <v>266464</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" s="4">
+        <v>278079</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
       <c r="A235" s="3">
-        <v>265822</v>
+        <v>273293</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2">
+        <v>247</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
       <c r="A236" s="3">
-        <v>266499</v>
+        <v>269965</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2">
+        <v>248</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
       <c r="A237" s="3">
-        <v>253776</v>
+        <v>258464</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2">
+        <v>249</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
       <c r="A238" s="3">
-        <v>270795</v>
+        <v>259796</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2">
-      <c r="A239" s="3">
-        <v>270784</v>
+        <v>250</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" s="4">
+        <v>276388</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2">
+        <v>251</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
       <c r="A240" s="3">
-        <v>271943</v>
+        <v>258455</v>
       </c>
       <c r="B240" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C240" s="4" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" spans="1:3">
       <c r="A241" s="3">
-        <v>247695</v>
+        <v>279511</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2">
+        <v>253</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
       <c r="A242" s="3">
-        <v>253781</v>
+        <v>246412</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2">
-      <c r="A243" s="3">
-        <v>211631</v>
+        <v>254</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" s="4">
+        <v>278647</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2">
-      <c r="A244" s="6">
-        <v>266464</v>
-      </c>
-      <c r="B244" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2">
-      <c r="A245" s="4">
-        <v>278079</v>
+        <v>255</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244" s="3">
+        <v>265803</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" s="3">
+        <v>259798</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2">
-      <c r="A246" s="4">
-        <v>281972</v>
+        <v>257</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="3">
+        <v>261757</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2">
-      <c r="A247" s="3">
-        <v>273293</v>
-      </c>
-      <c r="B247" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2">
+        <v>258</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="6">
+        <v>257611</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
       <c r="A248" s="3">
-        <v>276707</v>
+        <v>279512</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2">
-      <c r="A249" s="3">
-        <v>269965</v>
+        <v>260</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="4">
+        <v>273152</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2">
-      <c r="A250" s="3">
-        <v>258464</v>
+        <v>261</v>
+      </c>
+      <c r="C249" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" s="4">
+        <v>284046</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2">
-      <c r="A251" s="3">
-        <v>264179</v>
-      </c>
-      <c r="B251" s="4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2">
-      <c r="A252" s="3">
-        <v>259796</v>
+        <v>262</v>
+      </c>
+      <c r="C250" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" s="5">
+        <v>236219</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C251" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" s="4">
+        <v>277539</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2">
+        <v>264</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
       <c r="A253" s="4">
-        <v>276388</v>
+        <v>279453</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2">
-      <c r="A254" s="3">
-        <v>258455</v>
-      </c>
-      <c r="B254" s="4" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2">
+        <v>265</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" s="6">
+        <v>273291</v>
+      </c>
+      <c r="B254" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
       <c r="A255" s="3">
-        <v>279511</v>
+        <v>262054</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2">
+        <v>267</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
       <c r="A256" s="3">
-        <v>246412</v>
+        <v>274982</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2">
+        <v>268</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
       <c r="A257" s="4">
-        <v>278647</v>
+        <v>273421</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2">
-      <c r="A258" s="3">
-        <v>265803</v>
-      </c>
-      <c r="B258" s="4" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2">
+        <v>269</v>
+      </c>
+      <c r="C257" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" s="6">
+        <v>271948</v>
+      </c>
+      <c r="B258" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
       <c r="A259" s="3">
-        <v>259798</v>
+        <v>280959</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2">
-      <c r="A260" s="3">
-        <v>261757</v>
+        <v>271</v>
+      </c>
+      <c r="C259" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" s="4">
+        <v>278680</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2">
+        <v>272</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
       <c r="A261" s="4">
-        <v>278078</v>
+        <v>283735</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2">
-      <c r="A262" s="6">
-        <v>257611</v>
-      </c>
-      <c r="B262" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2">
-      <c r="A263" s="3">
-        <v>279512</v>
+        <v>273</v>
+      </c>
+      <c r="C261" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262" s="4">
+        <v>261777</v>
+      </c>
+      <c r="B262" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C262" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" s="4">
+        <v>280875</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2">
-      <c r="A264" s="4">
-        <v>273152</v>
-      </c>
-      <c r="B264" s="4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2">
+        <v>275</v>
+      </c>
+      <c r="C263" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" s="6">
+        <v>279540</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C264" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
       <c r="A265" s="4">
-        <v>284046</v>
+        <v>271879</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2">
-      <c r="A266" s="5">
-        <v>236219</v>
-      </c>
-      <c r="B266" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2">
-      <c r="A267" s="5">
-        <v>276035</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2">
+        <v>277</v>
+      </c>
+      <c r="C265" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" s="3">
+        <v>249564</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C266" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" s="4">
+        <v>215555</v>
+      </c>
+      <c r="B267" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C267" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
       <c r="A268" s="4">
-        <v>285839</v>
+        <v>280880</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2">
-      <c r="A269" s="4">
-        <v>277539</v>
+        <v>280</v>
+      </c>
+      <c r="C268" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269" s="3">
+        <v>213858</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="270" spans="1:2">
-      <c r="A270" s="4">
-        <v>279453</v>
+        <v>281</v>
+      </c>
+      <c r="C269" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" s="3">
+        <v>268097</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2">
-      <c r="A271" s="6">
-        <v>273291</v>
-      </c>
-      <c r="B271" s="7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2">
-      <c r="A272" s="3">
-        <v>262054</v>
+        <v>283</v>
+      </c>
+      <c r="C270" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" s="4">
+        <v>276385</v>
+      </c>
+      <c r="B271" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C271" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272" s="4">
+        <v>281970</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2">
+        <v>285</v>
+      </c>
+      <c r="C272" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
       <c r="A273" s="3">
-        <v>274982</v>
+        <v>263409</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2">
+        <v>286</v>
+      </c>
+      <c r="C273" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3">
       <c r="A274" s="4">
-        <v>273421</v>
+        <v>210531</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="275" spans="1:2">
-      <c r="A275" s="6">
-        <v>271948</v>
-      </c>
-      <c r="B275" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="276" spans="1:2">
-      <c r="A276" s="3">
-        <v>280959</v>
-      </c>
-      <c r="B276" s="4" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="277" spans="1:2">
-      <c r="A277" s="4">
-        <v>278680</v>
+        <v>287</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" s="4">
+        <v>276019</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="C275" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" s="6">
+        <v>272827</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C276" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" s="3">
+        <v>279043</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2">
-      <c r="A278" s="4">
-        <v>283735</v>
+        <v>290</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" s="3">
+        <v>246465</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2">
-      <c r="A279" s="3">
-        <v>249564</v>
+        <v>291</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" s="4">
+        <v>261778</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="280" spans="1:2">
+        <v>292</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
       <c r="A280" s="3">
-        <v>213858</v>
+        <v>270788</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="281" spans="1:2">
+        <v>293</v>
+      </c>
+      <c r="C280" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
       <c r="A281" s="3">
-        <v>268097</v>
+        <v>289953</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2">
+        <v>294</v>
+      </c>
+      <c r="C281" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
       <c r="A282" s="4">
-        <v>276385</v>
+        <v>285783</v>
       </c>
       <c r="B282" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C282" s="4" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
-      <c r="A283" s="4">
-        <v>281970</v>
-      </c>
-      <c r="B283" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2">
-      <c r="A284" s="3">
-        <v>263409</v>
-      </c>
-      <c r="B284" s="4" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2">
+    <row r="283" spans="1:3">
+      <c r="A283" s="6">
+        <v>284122</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C283" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" s="6">
+        <v>279543</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C284" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
       <c r="A285" s="4">
-        <v>210531</v>
+        <v>236145</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2">
+        <v>298</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
       <c r="A286" s="4">
-        <v>276019</v>
+        <v>264064</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2">
-      <c r="A287" s="4">
-        <v>215555</v>
-      </c>
-      <c r="B287" s="4" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2">
-      <c r="A288" s="6">
-        <v>272827</v>
-      </c>
-      <c r="B288" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2">
-      <c r="A289" s="3">
-        <v>279043</v>
-      </c>
-      <c r="B289" s="4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2">
-      <c r="A290" s="3">
-        <v>246465</v>
-      </c>
-      <c r="B290" s="4" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2">
-      <c r="A291" s="4">
-        <v>261778</v>
-      </c>
-      <c r="B291" s="4" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2">
+        <v>299</v>
+      </c>
+      <c r="C286" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" s="5">
+        <v>275099</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C287" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" s="5">
+        <v>282654</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289" s="5">
+        <v>274985</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290" s="6">
+        <v>282669</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291" s="6">
+        <v>282149</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
       <c r="A292" s="3">
-        <v>270788</v>
+        <v>280956</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2">
+        <v>305</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
       <c r="A293" s="3">
-        <v>289953</v>
+        <v>291328</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2">
-      <c r="A294" s="4">
-        <v>285783</v>
-      </c>
-      <c r="B294" s="4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2">
+        <v>306</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294" s="6">
+        <v>275109</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C294" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
       <c r="A295" s="6">
-        <v>284122</v>
-      </c>
-      <c r="B295" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2">
-      <c r="A296" s="4">
-        <v>280880</v>
+        <v>273295</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296" s="3">
+        <v>284048</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2">
-      <c r="A297" s="6">
-        <v>279543</v>
-      </c>
-      <c r="B297" s="6" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2">
-      <c r="A298" s="6">
-        <v>279540</v>
-      </c>
-      <c r="B298" s="6" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2">
-      <c r="A299" s="4">
-        <v>280875</v>
+        <v>309</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297" s="3">
+        <v>288733</v>
+      </c>
+      <c r="B297" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" s="3">
+        <v>211367</v>
+      </c>
+      <c r="B298" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C298" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" s="3">
+        <v>265617</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2">
-      <c r="A300" s="4">
-        <v>236145</v>
-      </c>
-      <c r="B300" s="4" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2">
-      <c r="A301" s="4">
-        <v>264064</v>
-      </c>
-      <c r="B301" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2">
-      <c r="A302" s="5">
-        <v>275099</v>
-      </c>
-      <c r="B302" s="5" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="303" spans="1:2">
-      <c r="A303" s="5">
-        <v>282654</v>
-      </c>
-      <c r="B303" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="304" spans="1:2">
-      <c r="A304" s="5">
-        <v>274985</v>
-      </c>
-      <c r="B304" s="5" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="305" spans="1:2">
-      <c r="A305" s="4">
-        <v>261777</v>
-      </c>
-      <c r="B305" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="306" spans="1:2">
-      <c r="A306" s="4">
-        <v>271879</v>
+        <v>312</v>
+      </c>
+      <c r="C299" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" s="6">
+        <v>278087</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C300" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301" s="6">
+        <v>283807</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C301" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302" s="3">
+        <v>283601</v>
+      </c>
+      <c r="B302" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C302" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" s="6">
+        <v>290978</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" s="4">
+        <v>272821</v>
+      </c>
+      <c r="B304" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C304" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" s="6">
+        <v>285277</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C305" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" s="3">
+        <v>284923</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="307" spans="1:2">
-      <c r="A307" s="6">
-        <v>282669</v>
-      </c>
-      <c r="B307" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="308" spans="1:2">
-      <c r="A308" s="6">
-        <v>282149</v>
-      </c>
-      <c r="B308" s="6" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="309" spans="1:2">
-      <c r="A309" s="3">
-        <v>280956</v>
-      </c>
-      <c r="B309" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="310" spans="1:2">
+        <v>319</v>
+      </c>
+      <c r="C306" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" s="5">
+        <v>275104</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" s="3">
+        <v>275006</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" s="6">
+        <v>294186</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
       <c r="A310" s="3">
-        <v>291328</v>
+        <v>266461</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="311" spans="1:2">
+        <v>323</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
       <c r="A311" s="6">
-        <v>275109</v>
-      </c>
-      <c r="B311" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="312" spans="1:2">
-      <c r="A312" s="6">
-        <v>273295</v>
-      </c>
-      <c r="B312" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="313" spans="1:2">
+        <v>298237</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312" s="3">
+        <v>275021</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
       <c r="A313" s="3">
-        <v>284048</v>
+        <v>283749</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="314" spans="1:2">
-      <c r="A314" s="3">
-        <v>288733</v>
-      </c>
-      <c r="B314" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="315" spans="1:2">
-      <c r="A315" s="3">
-        <v>211367</v>
+        <v>326</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" s="6">
+        <v>285896</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315" s="4">
+        <v>217602</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="316" spans="1:2">
+        <v>328</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
       <c r="A316" s="3">
-        <v>265617</v>
+        <v>276056</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="317" spans="1:2">
-      <c r="A317" s="6">
-        <v>278087</v>
-      </c>
-      <c r="B317" s="6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2">
-      <c r="A318" s="6">
-        <v>283807</v>
-      </c>
-      <c r="B318" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="319" spans="1:2">
-      <c r="A319" s="3">
-        <v>283601</v>
-      </c>
-      <c r="B319" s="4" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="320" spans="1:2">
-      <c r="A320" s="6">
-        <v>290978</v>
-      </c>
-      <c r="B320" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="321" spans="1:2">
-      <c r="A321" s="4">
-        <v>272821</v>
+        <v>329</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317" s="5">
+        <v>289669</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318" s="3">
+        <v>286123</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319" s="6">
+        <v>294185</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320" s="3">
+        <v>284330</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" s="3">
+        <v>284331</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
-      <c r="A322" s="6">
-        <v>285277</v>
-      </c>
-      <c r="B322" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="323" spans="1:2">
+        <v>335</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" s="3">
+        <v>284332</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
       <c r="A323" s="3">
-        <v>284923</v>
+        <v>291033</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="324" spans="1:2">
+        <v>337</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
       <c r="A324" s="5">
-        <v>275104</v>
+        <v>288902</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="325" spans="1:2">
-      <c r="A325" s="3">
-        <v>275006</v>
-      </c>
-      <c r="B325" s="4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="326" spans="1:2">
+        <v>338</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" s="6">
+        <v>292765</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
       <c r="A326" s="6">
-        <v>294186</v>
+        <v>281004</v>
       </c>
       <c r="B326" s="7" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="327" spans="1:2">
-      <c r="A327" s="3">
-        <v>266461</v>
-      </c>
-      <c r="B327" s="4" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="328" spans="1:2">
+        <v>340</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" s="6">
+        <v>278747</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
       <c r="A328" s="6">
-        <v>298237</v>
+        <v>263420</v>
       </c>
       <c r="B328" s="7" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="329" spans="1:2">
-      <c r="A329" s="3">
-        <v>275021</v>
-      </c>
-      <c r="B329" s="4" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="330" spans="1:2">
-      <c r="A330" s="3">
-        <v>283749</v>
-      </c>
-      <c r="B330" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="331" spans="1:2">
-      <c r="A331" s="4">
-        <v>217602</v>
-      </c>
-      <c r="B331" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="332" spans="1:2">
-      <c r="A332" s="3">
-        <v>284330</v>
-      </c>
-      <c r="B332" s="4" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="333" spans="1:2">
-      <c r="A333" s="3">
-        <v>284331</v>
-      </c>
-      <c r="B333" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="334" spans="1:2">
-      <c r="A334" s="3">
-        <v>284332</v>
-      </c>
-      <c r="B334" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C328" s="4" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="335" spans="1:2">
-      <c r="A335" s="3">
-        <v>291033</v>
-      </c>
-      <c r="B335" s="4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="336" spans="1:2">
+    <row r="329" spans="1:3">
+      <c r="A329" s="6">
+        <v>271929</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" s="6">
+        <v>273305</v>
+      </c>
+      <c r="B330" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" s="6">
+        <v>280074</v>
+      </c>
+      <c r="B331" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" s="6">
+        <v>278746</v>
+      </c>
+      <c r="B332" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" s="6">
+        <v>284201</v>
+      </c>
+      <c r="B333" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" s="6">
+        <v>276712</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" s="6">
+        <v>280145</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
       <c r="A336" s="6">
-        <v>285896</v>
-      </c>
-      <c r="B336" s="6" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2">
-      <c r="A337" s="3">
-        <v>286123</v>
-      </c>
-      <c r="B337" s="4" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2">
-      <c r="A338" s="3">
-        <v>276056</v>
-      </c>
-      <c r="B338" s="4" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2">
-      <c r="A339" s="5">
-        <v>288902</v>
-      </c>
-      <c r="B339" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2">
-      <c r="A340" s="5">
-        <v>289669</v>
-      </c>
-      <c r="B340" s="5" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2">
+        <v>280950</v>
+      </c>
+      <c r="B336" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" s="6">
+        <v>283833</v>
+      </c>
+      <c r="B337" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" s="6">
+        <v>294947</v>
+      </c>
+      <c r="B338" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" s="6">
+        <v>282686</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" s="6">
+        <v>282119</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
       <c r="A341" s="6">
-        <v>292765</v>
+        <v>294086</v>
       </c>
       <c r="B341" s="7" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2">
+        <v>355</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
       <c r="A342" s="6">
-        <v>281004</v>
+        <v>298124</v>
       </c>
       <c r="B342" s="7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2">
+        <v>356</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
       <c r="A343" s="6">
-        <v>278747</v>
+        <v>297287</v>
       </c>
       <c r="B343" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2">
+        <v>357</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
       <c r="A344" s="6">
-        <v>263420</v>
+        <v>297292</v>
       </c>
       <c r="B344" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2">
+        <v>358</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
       <c r="A345" s="6">
-        <v>271929</v>
+        <v>294511</v>
       </c>
       <c r="B345" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2">
+        <v>359</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
       <c r="A346" s="6">
-        <v>273305</v>
+        <v>298146</v>
       </c>
       <c r="B346" s="7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2">
+        <v>360</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
       <c r="A347" s="6">
-        <v>294185</v>
+        <v>273284</v>
       </c>
       <c r="B347" s="7" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2">
+        <v>361</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
       <c r="A348" s="6">
-        <v>280074</v>
+        <v>217693</v>
       </c>
       <c r="B348" s="7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2">
+        <v>362</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
       <c r="A349" s="6">
-        <v>278746</v>
+        <v>217703</v>
       </c>
       <c r="B349" s="7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2">
+        <v>363</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
       <c r="A350" s="6">
-        <v>284201</v>
+        <v>212877</v>
       </c>
       <c r="B350" s="7" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="351" spans="1:2">
+        <v>364</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
       <c r="A351" s="6">
-        <v>276712</v>
+        <v>306811</v>
       </c>
       <c r="B351" s="7" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2">
+        <v>365</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
       <c r="A352" s="6">
-        <v>280145</v>
+        <v>298838</v>
       </c>
       <c r="B352" s="7" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="353" spans="1:2">
+        <v>366</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
       <c r="A353" s="6">
-        <v>280950</v>
+        <v>302687</v>
       </c>
       <c r="B353" s="7" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="354" spans="1:2">
+        <v>367</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
       <c r="A354" s="6">
-        <v>283833</v>
+        <v>905147</v>
       </c>
       <c r="B354" s="7" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="355" spans="1:2">
+        <v>368</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
       <c r="A355" s="6">
-        <v>294947</v>
+        <v>249569</v>
       </c>
       <c r="B355" s="7" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="356" spans="1:2">
+        <v>369</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
       <c r="A356" s="6">
-        <v>282686</v>
+        <v>268080</v>
       </c>
       <c r="B356" s="7" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="357" spans="1:2">
+        <v>371</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
       <c r="A357" s="6">
-        <v>282119</v>
+        <v>906064</v>
       </c>
       <c r="B357" s="7" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="358" spans="1:2">
+        <v>372</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
       <c r="A358" s="6">
-        <v>294086</v>
+        <v>283744</v>
       </c>
       <c r="B358" s="7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="359" spans="1:2">
+        <v>373</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
       <c r="A359" s="6">
-        <v>298124</v>
+        <v>286107</v>
       </c>
       <c r="B359" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="360" spans="1:2">
+        <v>374</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
       <c r="A360" s="6">
-        <v>297287</v>
+        <v>288732</v>
       </c>
       <c r="B360" s="7" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="361" spans="1:2">
+        <v>375</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
       <c r="A361" s="6">
-        <v>297292</v>
+        <v>289565</v>
       </c>
       <c r="B361" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="362" spans="1:2">
-      <c r="A362" s="6">
-        <v>294511</v>
-      </c>
-      <c r="B362" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="363" spans="1:2">
-      <c r="A363" s="6">
-        <v>298146</v>
-      </c>
-      <c r="B363" s="7" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="364" spans="1:2">
-      <c r="A364" s="6">
-        <v>217693</v>
-      </c>
-      <c r="B364" s="7" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="365" spans="1:2">
-      <c r="A365" s="6">
-        <v>217703</v>
-      </c>
-      <c r="B365" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="366" spans="1:2">
-      <c r="A366" s="6">
-        <v>212877</v>
-      </c>
-      <c r="B366" s="7" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="367" spans="1:2">
-      <c r="A367" s="6">
-        <v>306811</v>
-      </c>
-      <c r="B367" s="7" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="368" spans="1:2">
-      <c r="A368" s="6">
-        <v>298838</v>
-      </c>
-      <c r="B368" s="7" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="369" spans="1:2">
-      <c r="A369" s="6">
-        <v>302687</v>
-      </c>
-      <c r="B369" s="7" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="370" spans="1:2">
-      <c r="A370" s="6">
-        <v>273284</v>
-      </c>
-      <c r="B370" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C361" s="4" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="371" spans="1:2">
-      <c r="A371" s="6">
-        <v>905147</v>
-      </c>
-      <c r="B371" s="7" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="372" spans="1:2">
-      <c r="A372" s="6">
-        <v>706596</v>
-      </c>
-      <c r="B372" s="7" t="s">
-        <v>372</v>
-      </c>
+    <row r="1048564" customFormat="1" spans="1:2">
+      <c r="A1048564" s="8"/>
+      <c r="B1048564" s="8"/>
+    </row>
+    <row r="1048565" customFormat="1" spans="1:2">
+      <c r="A1048565" s="8"/>
+      <c r="B1048565" s="8"/>
+    </row>
+    <row r="1048566" customFormat="1" spans="1:2">
+      <c r="A1048566" s="8"/>
+      <c r="B1048566" s="8"/>
+    </row>
+    <row r="1048567" customFormat="1" spans="1:2">
+      <c r="A1048567" s="8"/>
+      <c r="B1048567" s="8"/>
+    </row>
+    <row r="1048568" customFormat="1" spans="1:2">
+      <c r="A1048568" s="8"/>
+      <c r="B1048568" s="8"/>
+    </row>
+    <row r="1048569" customFormat="1" spans="1:2">
+      <c r="A1048569" s="8"/>
+      <c r="B1048569" s="8"/>
+    </row>
+    <row r="1048570" customFormat="1" spans="1:2">
+      <c r="A1048570" s="8"/>
+      <c r="B1048570" s="8"/>
+    </row>
+    <row r="1048571" customFormat="1" spans="1:2">
+      <c r="A1048571" s="8"/>
+      <c r="B1048571" s="8"/>
+    </row>
+    <row r="1048572" customFormat="1" spans="1:2">
+      <c r="A1048572" s="8"/>
+      <c r="B1048572" s="8"/>
+    </row>
+    <row r="1048573" customFormat="1" spans="1:2">
+      <c r="A1048573" s="8"/>
+      <c r="B1048573" s="8"/>
+    </row>
+    <row r="1048574" customFormat="1" spans="1:2">
+      <c r="A1048574" s="8"/>
+      <c r="B1048574" s="8"/>
+    </row>
+    <row r="1048575" customFormat="1" spans="1:2">
+      <c r="A1048575" s="8"/>
+      <c r="B1048575" s="8"/>
+    </row>
+    <row r="1048576" customFormat="1" spans="1:2">
+      <c r="A1048576" s="8"/>
+      <c r="B1048576" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B33 B37:B38 B373:B1048576 B47:B48 B40:B41 B45 B289:B290 B179 B185 B165:B167 B236:B249 B216:B227 B317:B320 B83 B315 B272 B310 B214 B188:B194 B100 B138:B141 B231:B234 B156:B157 B160:B163 B263:B265 B300:B307 B203:B209 B147:B149 B85:B86 B169:B170 B50:B74 B346 B102 B326:B327 B105:B135 B279:B280 B286:B287 B77:B81 B89 B323 B329:B335 B151:B153 B282:B283">
+  <conditionalFormatting sqref="B1048564:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B32 B44 B39:B40 B49 B46:B47 B36:B37 B77:B78 B51:B74 B79:B80 B84 B82 B99 B101 B96 B103:B104 B105:B107 B108:B109 B110:B112 B113:B114 B115:B121 B122:B125 B153 B167 B139:B141 B155:B158 B148:B151 B144:B145 B135:B137 B128:B129 B190:B194 B175:B181 B197 B306 B248:B250 B293 B262 B320:B323 B265:B267 B285:B290 B255 B219:B221 B312:B313 B309:B310 B330 B315 B199:B210 B214:B217 B300:B303 B298 B226:B236 B277:B278 B269 B362:B1048563 B271:B272 B275">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/template/机组花名册.xlsx
+++ b/public/template/机组花名册.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="25600" windowHeight="11630"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="401">
   <si>
     <t>员工号</t>
   </si>
@@ -278,6 +278,9 @@
     <t>张吉</t>
   </si>
   <si>
+    <t>闫珺熠</t>
+  </si>
+  <si>
     <t>张佳霖</t>
   </si>
   <si>
@@ -296,12 +299,18 @@
     <t>冀文龙</t>
   </si>
   <si>
+    <t>张勇</t>
+  </si>
+  <si>
     <t>陈志鹏</t>
   </si>
   <si>
     <t>刘作炫</t>
   </si>
   <si>
+    <t>薛杨</t>
+  </si>
+  <si>
     <t>罗建勇</t>
   </si>
   <si>
@@ -326,12 +335,24 @@
     <t>孙玉虎</t>
   </si>
   <si>
+    <t>罗竣艺</t>
+  </si>
+  <si>
     <t>方建斌</t>
   </si>
   <si>
     <t>张琪</t>
   </si>
   <si>
+    <t>王佳楠</t>
+  </si>
+  <si>
+    <t>丁汀</t>
+  </si>
+  <si>
+    <t>罗显涛</t>
+  </si>
+  <si>
     <t>Jochen Etienne L DE WISPELAERE</t>
   </si>
   <si>
@@ -359,6 +380,15 @@
     <t>邓龙</t>
   </si>
   <si>
+    <t>高思宇</t>
+  </si>
+  <si>
+    <t>蒋学隆</t>
+  </si>
+  <si>
+    <t>朱嘉俊</t>
+  </si>
+  <si>
     <t>陶炼</t>
   </si>
   <si>
@@ -377,6 +407,9 @@
     <t>彭程</t>
   </si>
   <si>
+    <t>冯志权</t>
+  </si>
+  <si>
     <t>李旭波</t>
   </si>
   <si>
@@ -392,6 +425,9 @@
     <t>张冀</t>
   </si>
   <si>
+    <t>龚智龙</t>
+  </si>
+  <si>
     <t>王彤阳</t>
   </si>
   <si>
@@ -413,6 +449,9 @@
     <t>张祺</t>
   </si>
   <si>
+    <t>刘超群</t>
+  </si>
+  <si>
     <t>连彦辉</t>
   </si>
   <si>
@@ -431,6 +470,9 @@
     <t>王琦</t>
   </si>
   <si>
+    <t>张雨</t>
+  </si>
+  <si>
     <t>胡佳欣</t>
   </si>
   <si>
@@ -443,9 +485,6 @@
     <t>Michiel Wouter Sebastiaan SCHOUTEN</t>
   </si>
   <si>
-    <t>丁汀</t>
-  </si>
-  <si>
     <t>陈建立</t>
   </si>
   <si>
@@ -461,9 +500,6 @@
     <t>杨昊</t>
   </si>
   <si>
-    <t>罗显涛</t>
-  </si>
-  <si>
     <t>熊寅</t>
   </si>
   <si>
@@ -578,6 +614,9 @@
     <t>崔玉柱</t>
   </si>
   <si>
+    <t>李晓波</t>
+  </si>
+  <si>
     <t>周思宁</t>
   </si>
   <si>
@@ -626,6 +665,18 @@
     <t>覃文添</t>
   </si>
   <si>
+    <t>吴智鑫</t>
+  </si>
+  <si>
+    <t>梁振</t>
+  </si>
+  <si>
+    <t>李正江</t>
+  </si>
+  <si>
+    <t>刘宇</t>
+  </si>
+  <si>
     <t>赵亚伟</t>
   </si>
   <si>
@@ -746,6 +797,12 @@
     <t>陈振浩</t>
   </si>
   <si>
+    <t>王程乾</t>
+  </si>
+  <si>
+    <t>田凯文</t>
+  </si>
+  <si>
     <t>陈兆铭</t>
   </si>
   <si>
@@ -764,9 +821,6 @@
     <t>周浩良</t>
   </si>
   <si>
-    <t>王程乾</t>
-  </si>
-  <si>
     <t>张子硕</t>
   </si>
   <si>
@@ -824,9 +878,6 @@
     <t>黄磊</t>
   </si>
   <si>
-    <t>田凯文</t>
-  </si>
-  <si>
     <t>袁皓华</t>
   </si>
   <si>
@@ -1115,15 +1166,6 @@
     <t>罗浩诚</t>
   </si>
   <si>
-    <t>吴智鑫</t>
-  </si>
-  <si>
-    <t>梁振</t>
-  </si>
-  <si>
-    <t>李正江</t>
-  </si>
-  <si>
     <t>聂莘欣</t>
   </si>
   <si>
@@ -1133,9 +1175,6 @@
     <t>孙金晨</t>
   </si>
   <si>
-    <t>刘宇</t>
-  </si>
-  <si>
     <t>吕博文</t>
   </si>
   <si>
@@ -1158,6 +1197,39 @@
   </si>
   <si>
     <t>杨宇轩</t>
+  </si>
+  <si>
+    <t>熊涛</t>
+  </si>
+  <si>
+    <t>时浩源</t>
+  </si>
+  <si>
+    <t>张展源</t>
+  </si>
+  <si>
+    <t>罗一凡</t>
+  </si>
+  <si>
+    <t>石志远</t>
+  </si>
+  <si>
+    <t>湛怀福</t>
+  </si>
+  <si>
+    <t>李旭</t>
+  </si>
+  <si>
+    <t>杨震</t>
+  </si>
+  <si>
+    <t>刘权</t>
+  </si>
+  <si>
+    <t>SHIM JAE HOON</t>
+  </si>
+  <si>
+    <t>划转机长</t>
   </si>
 </sst>
 </file>
@@ -1811,7 +1883,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1835,9 +1907,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2371,11 +2440,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <dimension ref="A1:C384"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="2" width="15.6272727272727" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="1" max="3" width="15.6272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3238,7 +3306,7 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="3">
-        <v>214335</v>
+        <v>216502</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>83</v>
@@ -3248,10 +3316,10 @@
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="5">
-        <v>202368</v>
-      </c>
-      <c r="B80" s="5" t="s">
+      <c r="A80" s="3">
+        <v>214335</v>
+      </c>
+      <c r="B80" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -3260,7 +3328,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="5">
-        <v>211430</v>
+        <v>202368</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>85</v>
@@ -3270,10 +3338,10 @@
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="3">
-        <v>215055</v>
-      </c>
-      <c r="B82" s="4" t="s">
+      <c r="A82" s="5">
+        <v>211430</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -3282,7 +3350,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="3">
-        <v>186643</v>
+        <v>215055</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>87</v>
@@ -3293,7 +3361,7 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="3">
-        <v>206748</v>
+        <v>186643</v>
       </c>
       <c r="B84" s="4" t="s">
         <v>88</v>
@@ -3303,10 +3371,10 @@
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="6">
-        <v>183002</v>
-      </c>
-      <c r="B85" s="7" t="s">
+      <c r="A85" s="3">
+        <v>206748</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C85" s="4" t="s">
@@ -3314,10 +3382,10 @@
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="6">
-        <v>207285</v>
-      </c>
-      <c r="B86" s="7" t="s">
+      <c r="A86" s="3">
+        <v>181851</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C86" s="4" t="s">
@@ -3326,7 +3394,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="6">
-        <v>202417</v>
+        <v>183002</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>91</v>
@@ -3337,7 +3405,7 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="6">
-        <v>208732</v>
+        <v>207285</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>92</v>
@@ -3347,10 +3415,10 @@
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="6">
-        <v>198204</v>
-      </c>
-      <c r="B89" s="7" t="s">
+      <c r="A89" s="4">
+        <v>901714</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C89" s="4" t="s">
@@ -3359,7 +3427,7 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="6">
-        <v>207623</v>
+        <v>202417</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>94</v>
@@ -3370,7 +3438,7 @@
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="6">
-        <v>213174</v>
+        <v>208732</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>95</v>
@@ -3381,7 +3449,7 @@
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="6">
-        <v>901785</v>
+        <v>198204</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>96</v>
@@ -3392,7 +3460,7 @@
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="6">
-        <v>181688</v>
+        <v>207623</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>97</v>
@@ -3402,10 +3470,10 @@
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="5">
-        <v>901621</v>
-      </c>
-      <c r="B94" s="5" t="s">
+      <c r="A94" s="6">
+        <v>213174</v>
+      </c>
+      <c r="B94" s="7" t="s">
         <v>98</v>
       </c>
       <c r="C94" s="4" t="s">
@@ -3414,7 +3482,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="6">
-        <v>186663</v>
+        <v>901785</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>99</v>
@@ -3424,2988 +3492,3186 @@
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="3">
-        <v>207621</v>
-      </c>
-      <c r="B96" s="4" t="s">
+      <c r="A96" s="6">
+        <v>181688</v>
+      </c>
+      <c r="B96" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="97" ht="42" spans="1:3">
-      <c r="A97" s="6">
+    <row r="97" spans="1:3">
+      <c r="A97" s="5">
+        <v>901621</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="3">
+        <v>210239</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="6">
+        <v>186663</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="3">
+        <v>207621</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="4">
+        <v>216750</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="3">
+        <v>210227</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="6">
+        <v>201138</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="104" ht="42" spans="1:3">
+      <c r="A104" s="6">
         <v>777575</v>
       </c>
-      <c r="B97" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="6">
+      <c r="B104" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="6">
         <v>771602</v>
       </c>
-      <c r="B98" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="3">
-        <v>215610</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="6">
-        <v>213091</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="3">
-        <v>213107</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="6">
-        <v>901531</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="3">
-        <v>216505</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="3">
-        <v>210899</v>
-      </c>
-      <c r="B104" s="4" t="s">
+      <c r="B105" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="3">
-        <v>210510</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="3">
-        <v>193177</v>
+        <v>215610</v>
       </c>
       <c r="B106" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="6">
+        <v>213091</v>
+      </c>
+      <c r="B107" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C106" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="3">
-        <v>202989</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="C107" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="3">
-        <v>208984</v>
+        <v>213107</v>
       </c>
       <c r="B108" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="6">
+        <v>901531</v>
+      </c>
+      <c r="B109" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C108" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="3">
-        <v>212810</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="C109" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="3">
-        <v>193238</v>
+        <v>216505</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="3">
-        <v>212914</v>
+        <v>210899</v>
       </c>
       <c r="B111" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="4">
+        <v>215060</v>
+      </c>
+      <c r="B112" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C111" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="3">
-        <v>196015</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="C112" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="3">
-        <v>206751</v>
+        <v>216757</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="3">
-        <v>193002</v>
+        <v>208978</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="3">
-        <v>212934</v>
+        <v>210510</v>
       </c>
       <c r="B115" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C115" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="3">
-        <v>196557</v>
+        <v>193177</v>
       </c>
       <c r="B116" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="3">
-        <v>211303</v>
+        <v>202989</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>123</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="3">
-        <v>212946</v>
+        <v>208984</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>124</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="3">
-        <v>708722</v>
+        <v>212810</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>125</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="3">
-        <v>210782</v>
+        <v>184767</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="3">
-        <v>210123</v>
+        <v>193238</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="3">
-        <v>202057</v>
+        <v>212914</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="3">
-        <v>211509</v>
+        <v>196015</v>
       </c>
       <c r="B123" s="4" t="s">
         <v>129</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="3">
-        <v>207632</v>
+        <v>206751</v>
       </c>
       <c r="B124" s="4" t="s">
         <v>130</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="3">
-        <v>189969</v>
+        <v>193002</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>131</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="5">
-        <v>211542</v>
-      </c>
-      <c r="B126" s="5" t="s">
+      <c r="A126" s="3">
+        <v>209990</v>
+      </c>
+      <c r="B126" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="5">
-        <v>612061</v>
-      </c>
-      <c r="B127" s="5" t="s">
+      <c r="A127" s="3">
+        <v>212934</v>
+      </c>
+      <c r="B127" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="4">
-        <v>224079</v>
+      <c r="A128" s="3">
+        <v>196557</v>
       </c>
       <c r="B128" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="3">
-        <v>218326</v>
+        <v>211303</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130" s="6">
-        <v>611893</v>
-      </c>
-      <c r="B130" s="7" t="s">
+      <c r="A130" s="3">
+        <v>212946</v>
+      </c>
+      <c r="B130" s="4" t="s">
         <v>136</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="131" ht="42" spans="1:3">
-      <c r="A131" s="6">
-        <v>263574</v>
-      </c>
-      <c r="B131" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="3">
+        <v>708722</v>
+      </c>
+      <c r="B131" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="3">
-        <v>210227</v>
+        <v>210782</v>
       </c>
       <c r="B132" s="4" t="s">
         <v>138</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="133" spans="1:3">
-      <c r="A133" s="6">
-        <v>181594</v>
-      </c>
-      <c r="B133" s="7" t="s">
+      <c r="A133" s="3">
+        <v>210123</v>
+      </c>
+      <c r="B133" s="4" t="s">
         <v>139</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="134" spans="1:3">
-      <c r="A134" s="6">
-        <v>196312</v>
-      </c>
-      <c r="B134" s="7" t="s">
+      <c r="A134" s="3">
+        <v>211566</v>
+      </c>
+      <c r="B134" s="4" t="s">
         <v>140</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="135" spans="1:3">
-      <c r="A135" s="4">
-        <v>211590</v>
+      <c r="A135" s="3">
+        <v>202057</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>141</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="3">
-        <v>192425</v>
+        <v>211509</v>
       </c>
       <c r="B136" s="4" t="s">
         <v>142</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="4">
-        <v>212660</v>
+      <c r="A137" s="3">
+        <v>207632</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>143</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="138" spans="1:3">
-      <c r="A138" s="6">
-        <v>201138</v>
-      </c>
-      <c r="B138" s="7" t="s">
+      <c r="A138" s="3">
+        <v>189969</v>
+      </c>
+      <c r="B138" s="4" t="s">
         <v>144</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="139" spans="1:3">
-      <c r="A139" s="3">
-        <v>212871</v>
-      </c>
-      <c r="B139" s="4" t="s">
+      <c r="A139" s="5">
+        <v>211542</v>
+      </c>
+      <c r="B139" s="5" t="s">
         <v>145</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="140" spans="1:3">
-      <c r="A140" s="4">
-        <v>206950</v>
-      </c>
-      <c r="B140" s="4" t="s">
+      <c r="A140" s="5">
+        <v>612061</v>
+      </c>
+      <c r="B140" s="5" t="s">
         <v>146</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141" spans="1:3">
-      <c r="A141" s="3">
-        <v>209259</v>
+      <c r="A141" s="4">
+        <v>215056</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>147</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="142" ht="28" spans="1:3">
-      <c r="A142" s="6">
-        <v>248809</v>
-      </c>
-      <c r="B142" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="4">
+        <v>224079</v>
+      </c>
+      <c r="B142" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="143" spans="1:3">
-      <c r="A143" s="6">
-        <v>213078</v>
-      </c>
-      <c r="B143" s="7" t="s">
+      <c r="A143" s="3">
+        <v>218326</v>
+      </c>
+      <c r="B143" s="4" t="s">
         <v>149</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="144" spans="1:3">
-      <c r="A144" s="4">
-        <v>217555</v>
-      </c>
-      <c r="B144" s="4" t="s">
+      <c r="A144" s="6">
+        <v>611893</v>
+      </c>
+      <c r="B144" s="7" t="s">
         <v>150</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3">
-      <c r="A145" s="4">
-        <v>206324</v>
-      </c>
-      <c r="B145" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="145" ht="42" spans="1:3">
+      <c r="A145" s="6">
+        <v>263574</v>
+      </c>
+      <c r="B145" s="7" t="s">
         <v>151</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="146" spans="1:3">
-      <c r="A146" s="3">
-        <v>217117</v>
-      </c>
-      <c r="B146" s="4" t="s">
+      <c r="A146" s="6">
+        <v>181594</v>
+      </c>
+      <c r="B146" s="7" t="s">
         <v>152</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="6">
-        <v>901500</v>
+        <v>196312</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>153</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="148" spans="1:3">
-      <c r="A148" s="3">
-        <v>195814</v>
+      <c r="A148" s="4">
+        <v>211590</v>
       </c>
       <c r="B148" s="4" t="s">
         <v>154</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="3">
-        <v>225674</v>
+        <v>192425</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>155</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="150" spans="1:3">
-      <c r="A150" s="3">
-        <v>186664</v>
+      <c r="A150" s="4">
+        <v>212660</v>
       </c>
       <c r="B150" s="4" t="s">
         <v>156</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151" s="3">
-        <v>234426</v>
+        <v>212871</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>157</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="152" spans="1:3">
-      <c r="A152" s="6">
-        <v>209178</v>
-      </c>
-      <c r="B152" s="7" t="s">
+      <c r="A152" s="4">
+        <v>206950</v>
+      </c>
+      <c r="B152" s="4" t="s">
         <v>158</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="153" spans="1:3">
-      <c r="A153" s="4">
-        <v>211558</v>
+      <c r="A153" s="3">
+        <v>209259</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>159</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3">
-      <c r="A154" s="3">
-        <v>217695</v>
-      </c>
-      <c r="B154" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="154" ht="28" spans="1:3">
+      <c r="A154" s="6">
+        <v>248809</v>
+      </c>
+      <c r="B154" s="7" t="s">
         <v>160</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="155" spans="1:3">
-      <c r="A155" s="3">
-        <v>188592</v>
-      </c>
-      <c r="B155" s="4" t="s">
+      <c r="A155" s="6">
+        <v>213078</v>
+      </c>
+      <c r="B155" s="7" t="s">
         <v>161</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156" s="4">
-        <v>211937</v>
+        <v>217555</v>
       </c>
       <c r="B156" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" s="4">
+        <v>206324</v>
+      </c>
+      <c r="B157" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3">
-      <c r="A157" s="3">
-        <v>208107</v>
-      </c>
-      <c r="B157" s="4" t="s">
+      <c r="C157" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="3">
+        <v>217117</v>
+      </c>
+      <c r="B158" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C157" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3">
-      <c r="A158" s="4">
-        <v>210767</v>
-      </c>
-      <c r="B158" s="4" t="s">
+      <c r="C158" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="6">
+        <v>901500</v>
+      </c>
+      <c r="B159" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C158" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3">
-      <c r="A159" s="3">
-        <v>903942</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="C159" s="4" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160" s="3">
-        <v>189186</v>
+        <v>195814</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161" s="3">
-        <v>905161</v>
+        <v>225674</v>
       </c>
       <c r="B161" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="3">
+        <v>186664</v>
+      </c>
+      <c r="B162" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C161" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162" s="6">
-        <v>192993</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="C162" s="4" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163" s="3">
-        <v>210155</v>
+        <v>234426</v>
       </c>
       <c r="B163" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="6">
+        <v>209178</v>
+      </c>
+      <c r="B164" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C163" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="3">
-        <v>901756</v>
-      </c>
-      <c r="B164" s="4" t="s">
+      <c r="C164" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="4">
+        <v>211558</v>
+      </c>
+      <c r="B165" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C164" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" s="3">
-        <v>901557</v>
-      </c>
-      <c r="B165" s="4" t="s">
+      <c r="C165" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="3">
+        <v>217695</v>
+      </c>
+      <c r="B166" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
-      <c r="A166" s="6">
-        <v>904950</v>
-      </c>
-      <c r="B166" s="7" t="s">
+      <c r="C166" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="3">
+        <v>188592</v>
+      </c>
+      <c r="B167" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
-      <c r="A167" s="4">
-        <v>210625</v>
-      </c>
-      <c r="B167" s="4" t="s">
+      <c r="C167" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C167" s="4" t="s">
-        <v>162</v>
-      </c>
     </row>
     <row r="168" spans="1:3">
-      <c r="A168" s="3">
-        <v>215073</v>
+      <c r="A168" s="4">
+        <v>211937</v>
       </c>
       <c r="B168" s="4" t="s">
         <v>175</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="5">
-        <v>184790</v>
-      </c>
-      <c r="B169" s="5" t="s">
+      <c r="A169" s="3">
+        <v>208107</v>
+      </c>
+      <c r="B169" s="4" t="s">
         <v>176</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="3">
-        <v>219807</v>
+      <c r="A170" s="4">
+        <v>210767</v>
       </c>
       <c r="B170" s="4" t="s">
         <v>177</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="171" spans="1:3">
-      <c r="A171" s="6">
-        <v>211588</v>
-      </c>
-      <c r="B171" s="7" t="s">
+      <c r="A171" s="3">
+        <v>903942</v>
+      </c>
+      <c r="B171" s="4" t="s">
         <v>178</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172" s="3">
-        <v>214908</v>
+        <v>189186</v>
       </c>
       <c r="B172" s="4" t="s">
         <v>179</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="3">
-        <v>211318</v>
+        <v>905161</v>
       </c>
       <c r="B173" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" s="6">
+        <v>192993</v>
+      </c>
+      <c r="B174" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C173" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3">
-      <c r="A174" s="3">
-        <v>210787</v>
-      </c>
-      <c r="B174" s="4" t="s">
+      <c r="C174" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" s="3">
+        <v>210155</v>
+      </c>
+      <c r="B175" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C174" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3">
-      <c r="A175" s="6">
-        <v>210135</v>
-      </c>
-      <c r="B175" s="7" t="s">
+      <c r="C175" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" s="3">
+        <v>901756</v>
+      </c>
+      <c r="B176" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C175" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3">
-      <c r="A176" s="6">
-        <v>210264</v>
-      </c>
-      <c r="B176" s="7" t="s">
+      <c r="C176" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" s="3">
+        <v>901557</v>
+      </c>
+      <c r="B177" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C176" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3">
-      <c r="A177" s="6">
-        <v>218359</v>
-      </c>
-      <c r="B177" s="7" t="s">
-        <v>185</v>
-      </c>
       <c r="C177" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178" s="6">
-        <v>211594</v>
+        <v>904950</v>
       </c>
       <c r="B178" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="4">
+        <v>210625</v>
+      </c>
+      <c r="B179" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C178" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3">
-      <c r="A179" s="6">
-        <v>224562</v>
-      </c>
-      <c r="B179" s="7" t="s">
+      <c r="C179" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" s="3">
+        <v>215073</v>
+      </c>
+      <c r="B180" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C179" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
-      <c r="A180" s="6">
-        <v>212815</v>
-      </c>
-      <c r="B180" s="7" t="s">
+      <c r="C180" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" s="5">
+        <v>184790</v>
+      </c>
+      <c r="B181" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C180" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3">
-      <c r="A181" s="6">
-        <v>189900</v>
-      </c>
-      <c r="B181" s="7" t="s">
+      <c r="C181" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="3">
+        <v>219807</v>
+      </c>
+      <c r="B182" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C181" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" s="6">
-        <v>217164</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>190</v>
-      </c>
       <c r="C182" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183" s="6">
-        <v>212657</v>
+        <v>211588</v>
       </c>
       <c r="B183" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" s="3">
+        <v>214908</v>
+      </c>
+      <c r="B184" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C183" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" s="6">
-        <v>213366</v>
-      </c>
-      <c r="B184" s="7" t="s">
+      <c r="C184" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C184" s="4" t="s">
-        <v>180</v>
-      </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="6">
-        <v>211575</v>
-      </c>
-      <c r="B185" s="7" t="s">
+      <c r="A185" s="3">
+        <v>211318</v>
+      </c>
+      <c r="B185" s="4" t="s">
         <v>193</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="186" spans="1:3">
-      <c r="A186" s="6">
-        <v>211407</v>
-      </c>
-      <c r="B186" s="7" t="s">
+      <c r="A186" s="3">
+        <v>210787</v>
+      </c>
+      <c r="B186" s="4" t="s">
         <v>194</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="187" spans="1:3">
-      <c r="A187" s="6">
-        <v>211410</v>
-      </c>
-      <c r="B187" s="7" t="s">
+      <c r="A187" s="3">
+        <v>205130</v>
+      </c>
+      <c r="B187" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188" s="6">
-        <v>211264</v>
+        <v>210135</v>
       </c>
       <c r="B188" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189" s="6">
-        <v>182998</v>
+        <v>210264</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>197</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="6">
-        <v>217707</v>
+        <v>218359</v>
       </c>
       <c r="B190" s="7" t="s">
         <v>198</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
     </row>
     <row r="191" spans="1:3">
-      <c r="A191" s="3">
+      <c r="A191" s="6">
+        <v>211594</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" s="6">
+        <v>224562</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3">
+      <c r="A193" s="6">
+        <v>212815</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
+      <c r="A194" s="6">
+        <v>189900</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3">
+      <c r="A195" s="6">
+        <v>217164</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3">
+      <c r="A196" s="6">
+        <v>212657</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3">
+      <c r="A197" s="6">
+        <v>213366</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3">
+      <c r="A198" s="6">
+        <v>211575</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3">
+      <c r="A199" s="6">
+        <v>211407</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3">
+      <c r="A200" s="6">
+        <v>211410</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3">
+      <c r="A201" s="6">
+        <v>211264</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3">
+      <c r="A202" s="6">
+        <v>182998</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3">
+      <c r="A203" s="6">
+        <v>217707</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3">
+      <c r="A204" s="6">
+        <v>217693</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3">
+      <c r="A205" s="6">
+        <v>217703</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3">
+      <c r="A206" s="6">
+        <v>212877</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
+      <c r="A207" s="6">
+        <v>905147</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3">
+      <c r="A208" s="3">
         <v>202379</v>
       </c>
-      <c r="B191" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3">
-      <c r="A192" s="3">
-        <v>240677</v>
-      </c>
-      <c r="B192" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3">
-      <c r="A193" s="3">
-        <v>259806</v>
-      </c>
-      <c r="B193" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3">
-      <c r="A194" s="3">
-        <v>236217</v>
-      </c>
-      <c r="B194" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3">
-      <c r="A195" s="3">
-        <v>248907</v>
-      </c>
-      <c r="B195" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3">
-      <c r="A196" s="3">
-        <v>260944</v>
-      </c>
-      <c r="B196" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3">
-      <c r="A197" s="3">
-        <v>257606</v>
-      </c>
-      <c r="B197" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3">
-      <c r="A198" s="3">
-        <v>251924</v>
-      </c>
-      <c r="B198" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3">
-      <c r="A199" s="3">
-        <v>273299</v>
-      </c>
-      <c r="B199" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3">
-      <c r="A200" s="3">
-        <v>230397</v>
-      </c>
-      <c r="B200" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3">
-      <c r="A201" s="3">
-        <v>248322</v>
-      </c>
-      <c r="B201" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3">
-      <c r="A202" s="3">
-        <v>248319</v>
-      </c>
-      <c r="B202" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3">
-      <c r="A203" s="3">
-        <v>258463</v>
-      </c>
-      <c r="B203" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3">
-      <c r="A204" s="3">
-        <v>261764</v>
-      </c>
-      <c r="B204" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3">
-      <c r="A205" s="3">
-        <v>262062</v>
-      </c>
-      <c r="B205" s="4" t="s">
+      <c r="B208" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C205" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3">
-      <c r="A206" s="3">
-        <v>265806</v>
-      </c>
-      <c r="B206" s="4" t="s">
+      <c r="C208" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3">
-      <c r="A207" s="3">
-        <v>265801</v>
-      </c>
-      <c r="B207" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3">
-      <c r="A208" s="6">
-        <v>210590</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" s="3">
-        <v>257603</v>
+        <v>240677</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210" s="3">
-        <v>253772</v>
+        <v>259806</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211" s="3">
-        <v>259803</v>
+        <v>236217</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212" s="3">
-        <v>263416</v>
+        <v>248907</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213" s="3">
-        <v>247704</v>
+        <v>260944</v>
       </c>
       <c r="B213" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" s="3">
+        <v>257606</v>
+      </c>
+      <c r="B214" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C213" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214" s="5">
-        <v>212982</v>
-      </c>
-      <c r="B214" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="C214" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215" s="3">
-        <v>271938</v>
+        <v>251924</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="3">
-        <v>282153</v>
+        <v>273299</v>
       </c>
       <c r="B216" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3">
+      <c r="A217" s="3">
+        <v>230397</v>
+      </c>
+      <c r="B217" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C216" s="4" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3">
-      <c r="A217" s="6">
-        <v>257697</v>
-      </c>
-      <c r="B217" s="6" t="s">
+      <c r="C217" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" s="3">
-        <v>265822</v>
+        <v>248322</v>
       </c>
       <c r="B218" s="4" t="s">
         <v>229</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="3">
-        <v>266499</v>
+        <v>248319</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>230</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="3">
-        <v>253776</v>
+        <v>258463</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>231</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="3">
-        <v>270795</v>
+        <v>261764</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>232</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="222" spans="1:3">
-      <c r="A222" s="5">
-        <v>276035</v>
-      </c>
-      <c r="B222" s="5" t="s">
+      <c r="A222" s="3">
+        <v>262062</v>
+      </c>
+      <c r="B222" s="4" t="s">
         <v>233</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="223" spans="1:3">
-      <c r="A223" s="4">
-        <v>285839</v>
+      <c r="A223" s="3">
+        <v>265806</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>234</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="224" spans="1:3">
-      <c r="A224" s="4">
-        <v>278078</v>
+      <c r="A224" s="3">
+        <v>265801</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>235</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="225" spans="1:3">
-      <c r="A225" s="3">
-        <v>264179</v>
-      </c>
-      <c r="B225" s="4" t="s">
+      <c r="A225" s="6">
+        <v>210590</v>
+      </c>
+      <c r="B225" s="6" t="s">
         <v>236</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="226" spans="1:3">
-      <c r="A226" s="4">
-        <v>281972</v>
+      <c r="A226" s="3">
+        <v>257603</v>
       </c>
       <c r="B226" s="4" t="s">
         <v>237</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" s="3">
-        <v>276707</v>
+        <v>253772</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>238</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="3">
-        <v>270784</v>
+        <v>259803</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>239</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="3">
-        <v>271943</v>
+        <v>263416</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="3">
-        <v>247695</v>
+        <v>247704</v>
       </c>
       <c r="B230" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231" s="5">
+        <v>212982</v>
+      </c>
+      <c r="B231" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C230" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3">
-      <c r="A231" s="3">
-        <v>253781</v>
-      </c>
-      <c r="B231" s="4" t="s">
-        <v>243</v>
-      </c>
       <c r="C231" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232" s="3">
-        <v>211631</v>
+        <v>271938</v>
       </c>
       <c r="B232" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233" s="3">
+        <v>282153</v>
+      </c>
+      <c r="B233" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C232" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
-      <c r="A233" s="6">
-        <v>266464</v>
-      </c>
-      <c r="B233" s="6" t="s">
+      <c r="C233" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234" s="6">
+        <v>257697</v>
+      </c>
+      <c r="B234" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C233" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3">
-      <c r="A234" s="4">
-        <v>278079</v>
-      </c>
-      <c r="B234" s="4" t="s">
-        <v>246</v>
-      </c>
       <c r="C234" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235" s="3">
-        <v>273293</v>
+        <v>265822</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236" s="3">
-        <v>269965</v>
+        <v>266499</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237" s="3">
-        <v>258464</v>
+        <v>253776</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238" s="3">
-        <v>259796</v>
+        <v>270795</v>
       </c>
       <c r="B238" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" s="5">
+        <v>276035</v>
+      </c>
+      <c r="B239" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C238" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
-      <c r="A239" s="4">
-        <v>276388</v>
-      </c>
-      <c r="B239" s="4" t="s">
+      <c r="C239" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" s="4">
+        <v>285839</v>
+      </c>
+      <c r="B240" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C239" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
-      <c r="A240" s="3">
-        <v>258455</v>
-      </c>
-      <c r="B240" s="4" t="s">
+      <c r="C240" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241" s="4">
+        <v>278078</v>
+      </c>
+      <c r="B241" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C240" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="3">
-        <v>279511</v>
-      </c>
-      <c r="B241" s="4" t="s">
-        <v>253</v>
-      </c>
       <c r="C241" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" s="3">
-        <v>246412</v>
+        <v>264179</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" s="4">
-        <v>278647</v>
+        <v>281972</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="3">
-        <v>265803</v>
+        <v>276707</v>
       </c>
       <c r="B244" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" s="6">
+        <v>266464</v>
+      </c>
+      <c r="B245" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="C244" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245" s="3">
-        <v>259798</v>
-      </c>
-      <c r="B245" s="4" t="s">
+      <c r="C245" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="4">
+        <v>279453</v>
+      </c>
+      <c r="B246" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C245" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" s="3">
-        <v>261757</v>
-      </c>
-      <c r="B246" s="4" t="s">
+      <c r="C246" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="3">
+        <v>270784</v>
+      </c>
+      <c r="B247" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C246" s="4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247" s="6">
-        <v>257611</v>
-      </c>
-      <c r="B247" s="6" t="s">
+      <c r="C247" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="C247" s="4" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="248" spans="1:3">
       <c r="A248" s="3">
-        <v>279512</v>
+        <v>271943</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>260</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="249" spans="1:3">
-      <c r="A249" s="4">
-        <v>273152</v>
+      <c r="A249" s="3">
+        <v>247695</v>
       </c>
       <c r="B249" s="4" t="s">
         <v>261</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="250" spans="1:3">
-      <c r="A250" s="4">
-        <v>284046</v>
+      <c r="A250" s="3">
+        <v>253781</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>262</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="5">
-        <v>236219</v>
-      </c>
-      <c r="B251" s="5" t="s">
+      <c r="A251" s="3">
+        <v>211631</v>
+      </c>
+      <c r="B251" s="4" t="s">
         <v>263</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="252" spans="1:3">
       <c r="A252" s="4">
-        <v>277539</v>
+        <v>278079</v>
       </c>
       <c r="B252" s="4" t="s">
         <v>264</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="253" spans="1:3">
-      <c r="A253" s="4">
-        <v>279453</v>
+      <c r="A253" s="3">
+        <v>273293</v>
       </c>
       <c r="B253" s="4" t="s">
         <v>265</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="254" spans="1:3">
-      <c r="A254" s="6">
-        <v>273291</v>
-      </c>
-      <c r="B254" s="7" t="s">
+      <c r="A254" s="3">
+        <v>269965</v>
+      </c>
+      <c r="B254" s="4" t="s">
         <v>266</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" s="3">
-        <v>262054</v>
+        <v>258464</v>
       </c>
       <c r="B255" s="4" t="s">
         <v>267</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" s="3">
-        <v>274982</v>
+        <v>259796</v>
       </c>
       <c r="B256" s="4" t="s">
         <v>268</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" s="4">
-        <v>273421</v>
+        <v>276388</v>
       </c>
       <c r="B257" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="258" spans="1:3">
-      <c r="A258" s="6">
-        <v>271948</v>
-      </c>
-      <c r="B258" s="7" t="s">
+      <c r="A258" s="3">
+        <v>258455</v>
+      </c>
+      <c r="B258" s="4" t="s">
         <v>270</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" s="3">
-        <v>280959</v>
+        <v>279511</v>
       </c>
       <c r="B259" s="4" t="s">
         <v>271</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="4">
-        <v>278680</v>
+      <c r="A260" s="3">
+        <v>246412</v>
       </c>
       <c r="B260" s="4" t="s">
         <v>272</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="261" spans="1:3">
       <c r="A261" s="4">
-        <v>283735</v>
+        <v>278647</v>
       </c>
       <c r="B261" s="4" t="s">
         <v>273</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="262" spans="1:3">
-      <c r="A262" s="4">
-        <v>261777</v>
+      <c r="A262" s="3">
+        <v>265803</v>
       </c>
       <c r="B262" s="4" t="s">
         <v>274</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="4">
-        <v>280875</v>
+      <c r="A263" s="3">
+        <v>259798</v>
       </c>
       <c r="B263" s="4" t="s">
         <v>275</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="264" spans="1:3">
-      <c r="A264" s="6">
-        <v>279540</v>
-      </c>
-      <c r="B264" s="6" t="s">
+      <c r="A264" s="3">
+        <v>261757</v>
+      </c>
+      <c r="B264" s="4" t="s">
         <v>276</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="265" spans="1:3">
-      <c r="A265" s="4">
-        <v>271879</v>
-      </c>
-      <c r="B265" s="4" t="s">
+      <c r="A265" s="6">
+        <v>257611</v>
+      </c>
+      <c r="B265" s="6" t="s">
         <v>277</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="266" spans="1:3">
       <c r="A266" s="3">
-        <v>249564</v>
+        <v>279512</v>
       </c>
       <c r="B266" s="4" t="s">
         <v>278</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="267" spans="1:3">
       <c r="A267" s="4">
-        <v>215555</v>
+        <v>273152</v>
       </c>
       <c r="B267" s="4" t="s">
         <v>279</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="268" spans="1:3">
       <c r="A268" s="4">
-        <v>280880</v>
+        <v>284046</v>
       </c>
       <c r="B268" s="4" t="s">
         <v>280</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="269" spans="1:3">
-      <c r="A269" s="3">
-        <v>213858</v>
-      </c>
-      <c r="B269" s="4" t="s">
+      <c r="A269" s="5">
+        <v>236219</v>
+      </c>
+      <c r="B269" s="5" t="s">
         <v>281</v>
       </c>
       <c r="C269" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" s="4">
+        <v>277539</v>
+      </c>
+      <c r="B270" s="4" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="270" spans="1:3">
-      <c r="A270" s="3">
-        <v>268097</v>
-      </c>
-      <c r="B270" s="4" t="s">
+      <c r="C270" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" s="6">
+        <v>273291</v>
+      </c>
+      <c r="B271" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="C270" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3">
-      <c r="A271" s="4">
-        <v>276385</v>
-      </c>
-      <c r="B271" s="4" t="s">
+      <c r="C271" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272" s="3">
+        <v>262054</v>
+      </c>
+      <c r="B272" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C271" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3">
-      <c r="A272" s="4">
-        <v>281970</v>
-      </c>
-      <c r="B272" s="4" t="s">
-        <v>285</v>
-      </c>
       <c r="C272" s="4" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" s="3">
-        <v>263409</v>
+        <v>274982</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" s="4">
-        <v>210531</v>
+        <v>273421</v>
       </c>
       <c r="B274" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C274" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" s="6">
+        <v>271948</v>
+      </c>
+      <c r="B275" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C274" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3">
-      <c r="A275" s="4">
-        <v>276019</v>
-      </c>
-      <c r="B275" s="4" t="s">
+      <c r="C275" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" s="3">
+        <v>280959</v>
+      </c>
+      <c r="B276" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C275" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3">
-      <c r="A276" s="6">
-        <v>272827</v>
-      </c>
-      <c r="B276" s="6" t="s">
+      <c r="C276" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" s="4">
+        <v>278680</v>
+      </c>
+      <c r="B277" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C276" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3">
-      <c r="A277" s="3">
-        <v>279043</v>
-      </c>
-      <c r="B277" s="4" t="s">
+      <c r="C277" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" s="4">
+        <v>283735</v>
+      </c>
+      <c r="B278" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C277" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3">
-      <c r="A278" s="3">
-        <v>246465</v>
-      </c>
-      <c r="B278" s="4" t="s">
-        <v>291</v>
-      </c>
       <c r="C278" s="4" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
     </row>
     <row r="279" spans="1:3">
       <c r="A279" s="4">
-        <v>261778</v>
+        <v>261777</v>
       </c>
       <c r="B279" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C279" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" s="4">
+        <v>280875</v>
+      </c>
+      <c r="B280" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C279" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3">
-      <c r="A280" s="3">
-        <v>270788</v>
-      </c>
-      <c r="B280" s="4" t="s">
+      <c r="C280" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" s="6">
+        <v>279540</v>
+      </c>
+      <c r="B281" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="C280" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3">
-      <c r="A281" s="3">
-        <v>289953</v>
-      </c>
-      <c r="B281" s="4" t="s">
-        <v>294</v>
-      </c>
       <c r="C281" s="4" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
     </row>
     <row r="282" spans="1:3">
       <c r="A282" s="4">
-        <v>285783</v>
+        <v>271879</v>
       </c>
       <c r="B282" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C282" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283" s="3">
+        <v>249564</v>
+      </c>
+      <c r="B283" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="C282" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3">
-      <c r="A283" s="6">
-        <v>284122</v>
-      </c>
-      <c r="B283" s="6" t="s">
+      <c r="C283" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" s="4">
+        <v>215555</v>
+      </c>
+      <c r="B284" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C283" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3">
-      <c r="A284" s="6">
-        <v>279543</v>
-      </c>
-      <c r="B284" s="6" t="s">
-        <v>297</v>
-      </c>
       <c r="C284" s="4" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" s="4">
-        <v>236145</v>
+        <v>280880</v>
       </c>
       <c r="B285" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C285" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286" s="3">
+        <v>213858</v>
+      </c>
+      <c r="B286" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="C285" s="4" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3">
-      <c r="A286" s="4">
-        <v>264064</v>
-      </c>
-      <c r="B286" s="4" t="s">
+      <c r="C286" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C286" s="4" t="s">
-        <v>282</v>
-      </c>
     </row>
     <row r="287" spans="1:3">
-      <c r="A287" s="5">
-        <v>275099</v>
-      </c>
-      <c r="B287" s="5" t="s">
+      <c r="A287" s="3">
+        <v>268097</v>
+      </c>
+      <c r="B287" s="4" t="s">
         <v>300</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="288" spans="1:3">
-      <c r="A288" s="5">
-        <v>282654</v>
-      </c>
-      <c r="B288" s="5" t="s">
+      <c r="A288" s="4">
+        <v>276385</v>
+      </c>
+      <c r="B288" s="4" t="s">
         <v>301</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="289" spans="1:3">
-      <c r="A289" s="5">
-        <v>274985</v>
-      </c>
-      <c r="B289" s="5" t="s">
+      <c r="A289" s="4">
+        <v>281970</v>
+      </c>
+      <c r="B289" s="4" t="s">
         <v>302</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="290" spans="1:3">
-      <c r="A290" s="6">
-        <v>282669</v>
-      </c>
-      <c r="B290" s="6" t="s">
+      <c r="A290" s="3">
+        <v>263409</v>
+      </c>
+      <c r="B290" s="4" t="s">
         <v>303</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="291" spans="1:3">
-      <c r="A291" s="6">
-        <v>282149</v>
-      </c>
-      <c r="B291" s="6" t="s">
+      <c r="A291" s="4">
+        <v>210531</v>
+      </c>
+      <c r="B291" s="4" t="s">
         <v>304</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="292" spans="1:3">
-      <c r="A292" s="3">
-        <v>280956</v>
+      <c r="A292" s="4">
+        <v>276019</v>
       </c>
       <c r="B292" s="4" t="s">
         <v>305</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="293" spans="1:3">
-      <c r="A293" s="3">
-        <v>291328</v>
-      </c>
-      <c r="B293" s="4" t="s">
+      <c r="A293" s="6">
+        <v>272827</v>
+      </c>
+      <c r="B293" s="6" t="s">
         <v>306</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="294" spans="1:3">
-      <c r="A294" s="6">
-        <v>275109</v>
-      </c>
-      <c r="B294" s="6" t="s">
+      <c r="A294" s="3">
+        <v>279043</v>
+      </c>
+      <c r="B294" s="4" t="s">
         <v>307</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="6">
-        <v>273295</v>
-      </c>
-      <c r="B295" s="7" t="s">
+      <c r="A295" s="3">
+        <v>246465</v>
+      </c>
+      <c r="B295" s="4" t="s">
         <v>308</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="3">
-        <v>284048</v>
+      <c r="A296" s="4">
+        <v>261778</v>
       </c>
       <c r="B296" s="4" t="s">
         <v>309</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" s="3">
-        <v>288733</v>
+        <v>270788</v>
       </c>
       <c r="B297" s="4" t="s">
         <v>310</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" s="3">
-        <v>211367</v>
+        <v>289953</v>
       </c>
       <c r="B298" s="4" t="s">
         <v>311</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="299" spans="1:3">
-      <c r="A299" s="3">
-        <v>265617</v>
+      <c r="A299" s="4">
+        <v>285783</v>
       </c>
       <c r="B299" s="4" t="s">
         <v>312</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" s="6">
-        <v>278087</v>
+        <v>284122</v>
       </c>
       <c r="B300" s="6" t="s">
         <v>313</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" s="6">
-        <v>283807</v>
-      </c>
-      <c r="B301" s="7" t="s">
+        <v>279543</v>
+      </c>
+      <c r="B301" s="6" t="s">
         <v>314</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="302" spans="1:3">
-      <c r="A302" s="3">
-        <v>283601</v>
+      <c r="A302" s="4">
+        <v>236145</v>
       </c>
       <c r="B302" s="4" t="s">
         <v>315</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="6">
-        <v>290978</v>
-      </c>
-      <c r="B303" s="6" t="s">
+      <c r="A303" s="4">
+        <v>264064</v>
+      </c>
+      <c r="B303" s="4" t="s">
         <v>316</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="4">
-        <v>272821</v>
-      </c>
-      <c r="B304" s="4" t="s">
+      <c r="A304" s="5">
+        <v>275099</v>
+      </c>
+      <c r="B304" s="5" t="s">
         <v>317</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="305" spans="1:3">
-      <c r="A305" s="6">
-        <v>285277</v>
-      </c>
-      <c r="B305" s="6" t="s">
+      <c r="A305" s="5">
+        <v>282654</v>
+      </c>
+      <c r="B305" s="5" t="s">
         <v>318</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="306" spans="1:3">
-      <c r="A306" s="3">
-        <v>284923</v>
-      </c>
-      <c r="B306" s="4" t="s">
+      <c r="A306" s="5">
+        <v>274985</v>
+      </c>
+      <c r="B306" s="5" t="s">
         <v>319</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="307" spans="1:3">
-      <c r="A307" s="5">
-        <v>275104</v>
-      </c>
-      <c r="B307" s="5" t="s">
+      <c r="A307" s="6">
+        <v>282669</v>
+      </c>
+      <c r="B307" s="6" t="s">
         <v>320</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="308" spans="1:3">
-      <c r="A308" s="3">
-        <v>275006</v>
-      </c>
-      <c r="B308" s="4" t="s">
+      <c r="A308" s="6">
+        <v>282149</v>
+      </c>
+      <c r="B308" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="309" spans="1:3">
-      <c r="A309" s="6">
-        <v>294186</v>
-      </c>
-      <c r="B309" s="7" t="s">
+      <c r="A309" s="3">
+        <v>280956</v>
+      </c>
+      <c r="B309" s="4" t="s">
         <v>322</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="310" spans="1:3">
       <c r="A310" s="3">
-        <v>266461</v>
+        <v>291328</v>
       </c>
       <c r="B310" s="4" t="s">
         <v>323</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="311" spans="1:3">
       <c r="A311" s="6">
-        <v>298237</v>
-      </c>
-      <c r="B311" s="7" t="s">
+        <v>275109</v>
+      </c>
+      <c r="B311" s="6" t="s">
         <v>324</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="3">
-        <v>275021</v>
-      </c>
-      <c r="B312" s="4" t="s">
+      <c r="A312" s="6">
+        <v>273295</v>
+      </c>
+      <c r="B312" s="7" t="s">
         <v>325</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="3">
-        <v>283749</v>
+        <v>284048</v>
       </c>
       <c r="B313" s="4" t="s">
         <v>326</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="314" spans="1:3">
-      <c r="A314" s="6">
-        <v>285896</v>
-      </c>
-      <c r="B314" s="6" t="s">
+      <c r="A314" s="3">
+        <v>288733</v>
+      </c>
+      <c r="B314" s="4" t="s">
         <v>327</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="315" spans="1:3">
-      <c r="A315" s="4">
-        <v>217602</v>
+      <c r="A315" s="3">
+        <v>211367</v>
       </c>
       <c r="B315" s="4" t="s">
         <v>328</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="316" spans="1:3">
       <c r="A316" s="3">
-        <v>276056</v>
+        <v>265617</v>
       </c>
       <c r="B316" s="4" t="s">
         <v>329</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="317" spans="1:3">
-      <c r="A317" s="5">
-        <v>289669</v>
-      </c>
-      <c r="B317" s="5" t="s">
+      <c r="A317" s="6">
+        <v>278087</v>
+      </c>
+      <c r="B317" s="6" t="s">
         <v>330</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="318" spans="1:3">
-      <c r="A318" s="3">
-        <v>286123</v>
-      </c>
-      <c r="B318" s="4" t="s">
+      <c r="A318" s="6">
+        <v>283807</v>
+      </c>
+      <c r="B318" s="7" t="s">
         <v>331</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="319" spans="1:3">
-      <c r="A319" s="6">
-        <v>294185</v>
-      </c>
-      <c r="B319" s="7" t="s">
+      <c r="A319" s="3">
+        <v>283601</v>
+      </c>
+      <c r="B319" s="4" t="s">
         <v>332</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="320" spans="1:3">
-      <c r="A320" s="3">
-        <v>284330</v>
-      </c>
-      <c r="B320" s="4" t="s">
+      <c r="A320" s="6">
+        <v>290978</v>
+      </c>
+      <c r="B320" s="6" t="s">
         <v>333</v>
       </c>
       <c r="C320" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" s="4">
+        <v>272821</v>
+      </c>
+      <c r="B321" s="4" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="321" spans="1:3">
-      <c r="A321" s="3">
-        <v>284331</v>
-      </c>
-      <c r="B321" s="4" t="s">
+      <c r="C321" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" s="6">
+        <v>285277</v>
+      </c>
+      <c r="B322" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="C321" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3">
-      <c r="A322" s="3">
-        <v>284332</v>
-      </c>
-      <c r="B322" s="4" t="s">
-        <v>336</v>
-      </c>
       <c r="C322" s="4" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" s="3">
-        <v>291033</v>
+        <v>284923</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
     </row>
     <row r="324" spans="1:3">
       <c r="A324" s="5">
-        <v>288902</v>
+        <v>275104</v>
       </c>
       <c r="B324" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" s="3">
+        <v>275006</v>
+      </c>
+      <c r="B325" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="C324" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3">
-      <c r="A325" s="6">
-        <v>292765</v>
-      </c>
-      <c r="B325" s="7" t="s">
-        <v>339</v>
-      </c>
       <c r="C325" s="4" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
     </row>
     <row r="326" spans="1:3">
       <c r="A326" s="6">
-        <v>281004</v>
+        <v>294186</v>
       </c>
       <c r="B326" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" s="3">
+        <v>266461</v>
+      </c>
+      <c r="B327" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="C326" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3">
-      <c r="A327" s="6">
-        <v>278747</v>
-      </c>
-      <c r="B327" s="7" t="s">
-        <v>341</v>
-      </c>
       <c r="C327" s="4" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
     </row>
     <row r="328" spans="1:3">
       <c r="A328" s="6">
-        <v>263420</v>
+        <v>298237</v>
       </c>
       <c r="B328" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" s="3">
+        <v>275021</v>
+      </c>
+      <c r="B329" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="C328" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3">
-      <c r="A329" s="6">
-        <v>271929</v>
-      </c>
-      <c r="B329" s="7" t="s">
+      <c r="C329" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" s="3">
+        <v>283749</v>
+      </c>
+      <c r="B330" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="C329" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3">
-      <c r="A330" s="6">
-        <v>273305</v>
-      </c>
-      <c r="B330" s="7" t="s">
-        <v>344</v>
-      </c>
       <c r="C330" s="4" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" s="6">
-        <v>280074</v>
-      </c>
-      <c r="B331" s="7" t="s">
+        <v>285896</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" s="4">
+        <v>217602</v>
+      </c>
+      <c r="B332" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C331" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3">
-      <c r="A332" s="6">
-        <v>278746</v>
-      </c>
-      <c r="B332" s="7" t="s">
+      <c r="C332" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" s="3">
+        <v>276056</v>
+      </c>
+      <c r="B333" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="C332" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3">
-      <c r="A333" s="6">
-        <v>284201</v>
-      </c>
-      <c r="B333" s="7" t="s">
+      <c r="C333" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" s="5">
+        <v>289669</v>
+      </c>
+      <c r="B334" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="C333" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3">
-      <c r="A334" s="6">
-        <v>276712</v>
-      </c>
-      <c r="B334" s="7" t="s">
+      <c r="C334" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" s="3">
+        <v>286123</v>
+      </c>
+      <c r="B335" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="C334" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3">
-      <c r="A335" s="6">
-        <v>280145</v>
-      </c>
-      <c r="B335" s="7" t="s">
-        <v>349</v>
-      </c>
       <c r="C335" s="4" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
     </row>
     <row r="336" spans="1:3">
       <c r="A336" s="6">
-        <v>280950</v>
+        <v>294185</v>
       </c>
       <c r="B336" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" s="3">
+        <v>284330</v>
+      </c>
+      <c r="B337" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="C336" s="4" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3">
-      <c r="A337" s="6">
-        <v>283833</v>
-      </c>
-      <c r="B337" s="7" t="s">
+      <c r="C337" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="C337" s="4" t="s">
-        <v>334</v>
-      </c>
     </row>
     <row r="338" spans="1:3">
-      <c r="A338" s="6">
-        <v>294947</v>
-      </c>
-      <c r="B338" s="7" t="s">
+      <c r="A338" s="3">
+        <v>284331</v>
+      </c>
+      <c r="B338" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="339" spans="1:3">
-      <c r="A339" s="6">
-        <v>282686</v>
-      </c>
-      <c r="B339" s="7" t="s">
+      <c r="A339" s="3">
+        <v>284332</v>
+      </c>
+      <c r="B339" s="4" t="s">
         <v>353</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="340" spans="1:3">
-      <c r="A340" s="6">
-        <v>282119</v>
-      </c>
-      <c r="B340" s="7" t="s">
+      <c r="A340" s="3">
+        <v>291033</v>
+      </c>
+      <c r="B340" s="4" t="s">
         <v>354</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="341" spans="1:3">
-      <c r="A341" s="6">
-        <v>294086</v>
-      </c>
-      <c r="B341" s="7" t="s">
+      <c r="A341" s="5">
+        <v>288902</v>
+      </c>
+      <c r="B341" s="5" t="s">
         <v>355</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="342" spans="1:3">
       <c r="A342" s="6">
-        <v>298124</v>
+        <v>292765</v>
       </c>
       <c r="B342" s="7" t="s">
         <v>356</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" s="6">
-        <v>297287</v>
+        <v>281004</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>357</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" s="6">
-        <v>297292</v>
+        <v>278747</v>
       </c>
       <c r="B344" s="7" t="s">
         <v>358</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" s="6">
-        <v>294511</v>
+        <v>263420</v>
       </c>
       <c r="B345" s="7" t="s">
         <v>359</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="6">
-        <v>298146</v>
+        <v>271929</v>
       </c>
       <c r="B346" s="7" t="s">
         <v>360</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" s="6">
-        <v>273284</v>
+        <v>273305</v>
       </c>
       <c r="B347" s="7" t="s">
         <v>361</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" s="6">
-        <v>217693</v>
+        <v>280074</v>
       </c>
       <c r="B348" s="7" t="s">
         <v>362</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>180</v>
+        <v>351</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" s="6">
-        <v>217703</v>
+        <v>278746</v>
       </c>
       <c r="B349" s="7" t="s">
         <v>363</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>180</v>
+        <v>351</v>
       </c>
     </row>
     <row r="350" spans="1:3">
       <c r="A350" s="6">
-        <v>212877</v>
+        <v>284201</v>
       </c>
       <c r="B350" s="7" t="s">
         <v>364</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>180</v>
+        <v>351</v>
       </c>
     </row>
     <row r="351" spans="1:3">
       <c r="A351" s="6">
-        <v>306811</v>
+        <v>276712</v>
       </c>
       <c r="B351" s="7" t="s">
         <v>365</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" s="6">
-        <v>298838</v>
+        <v>280145</v>
       </c>
       <c r="B352" s="7" t="s">
         <v>366</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" s="6">
-        <v>302687</v>
+        <v>280950</v>
       </c>
       <c r="B353" s="7" t="s">
         <v>367</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="6">
-        <v>905147</v>
+        <v>283833</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>368</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>180</v>
+        <v>351</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" s="6">
-        <v>249569</v>
+        <v>294947</v>
       </c>
       <c r="B355" s="7" t="s">
         <v>369</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" s="6">
-        <v>268080</v>
+        <v>282686</v>
       </c>
       <c r="B356" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" s="6">
-        <v>906064</v>
+        <v>282119</v>
       </c>
       <c r="B357" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" s="6">
-        <v>283744</v>
+        <v>294086</v>
       </c>
       <c r="B358" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" s="6">
-        <v>286107</v>
+        <v>298124</v>
       </c>
       <c r="B359" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" s="6">
-        <v>288732</v>
+        <v>297287</v>
       </c>
       <c r="B360" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" s="6">
+        <v>297292</v>
+      </c>
+      <c r="B361" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362" s="6">
+        <v>294511</v>
+      </c>
+      <c r="B362" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363" s="6">
+        <v>298146</v>
+      </c>
+      <c r="B363" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C363" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364" s="6">
+        <v>273284</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C364" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365" s="6">
+        <v>306811</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="C365" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366" s="6">
+        <v>298838</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C366" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367" s="6">
+        <v>302687</v>
+      </c>
+      <c r="B367" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C367" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368" s="6">
+        <v>249569</v>
+      </c>
+      <c r="B368" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="C368" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369" s="6">
+        <v>268080</v>
+      </c>
+      <c r="B369" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370" s="6">
+        <v>906064</v>
+      </c>
+      <c r="B370" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371" s="6">
+        <v>283744</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372" s="6">
+        <v>286107</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373" s="6">
+        <v>288732</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374" s="6">
         <v>289565</v>
       </c>
-      <c r="B361" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="C361" s="4" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="1048564" customFormat="1" spans="1:2">
-      <c r="A1048564" s="8"/>
-      <c r="B1048564" s="8"/>
-    </row>
-    <row r="1048565" customFormat="1" spans="1:2">
-      <c r="A1048565" s="8"/>
-      <c r="B1048565" s="8"/>
-    </row>
-    <row r="1048566" customFormat="1" spans="1:2">
-      <c r="A1048566" s="8"/>
-      <c r="B1048566" s="8"/>
-    </row>
-    <row r="1048567" customFormat="1" spans="1:2">
-      <c r="A1048567" s="8"/>
-      <c r="B1048567" s="8"/>
-    </row>
-    <row r="1048568" customFormat="1" spans="1:2">
-      <c r="A1048568" s="8"/>
-      <c r="B1048568" s="8"/>
-    </row>
-    <row r="1048569" customFormat="1" spans="1:2">
-      <c r="A1048569" s="8"/>
-      <c r="B1048569" s="8"/>
-    </row>
-    <row r="1048570" customFormat="1" spans="1:2">
-      <c r="A1048570" s="8"/>
-      <c r="B1048570" s="8"/>
-    </row>
-    <row r="1048571" customFormat="1" spans="1:2">
-      <c r="A1048571" s="8"/>
-      <c r="B1048571" s="8"/>
-    </row>
-    <row r="1048572" customFormat="1" spans="1:2">
-      <c r="A1048572" s="8"/>
-      <c r="B1048572" s="8"/>
-    </row>
-    <row r="1048573" customFormat="1" spans="1:2">
-      <c r="A1048573" s="8"/>
-      <c r="B1048573" s="8"/>
-    </row>
-    <row r="1048574" customFormat="1" spans="1:2">
-      <c r="A1048574" s="8"/>
-      <c r="B1048574" s="8"/>
-    </row>
-    <row r="1048575" customFormat="1" spans="1:2">
-      <c r="A1048575" s="8"/>
-      <c r="B1048575" s="8"/>
-    </row>
-    <row r="1048576" customFormat="1" spans="1:2">
-      <c r="A1048576" s="8"/>
-      <c r="B1048576" s="8"/>
+      <c r="B374" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375" s="6">
+        <v>294936</v>
+      </c>
+      <c r="B375" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" s="6">
+        <v>282016</v>
+      </c>
+      <c r="B376" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" s="6">
+        <v>298179</v>
+      </c>
+      <c r="B377" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" s="6">
+        <v>302250</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" s="6">
+        <v>303204</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380" s="6">
+        <v>302251</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381" s="6">
+        <v>302252</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" s="6">
+        <v>303944</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383" s="6">
+        <v>302249</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384" s="6">
+        <v>326411</v>
+      </c>
+      <c r="B384" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>400</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1048564:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B32 B44 B39:B40 B49 B46:B47 B36:B37 B77:B78 B51:B74 B79:B80 B84 B82 B99 B101 B96 B103:B104 B105:B107 B108:B109 B110:B112 B113:B114 B115:B121 B122:B125 B153 B167 B139:B141 B155:B158 B148:B151 B144:B145 B135:B137 B128:B129 B190:B194 B175:B181 B197 B306 B248:B250 B293 B262 B320:B323 B265:B267 B285:B290 B255 B219:B221 B312:B313 B309:B310 B330 B315 B199:B210 B214:B217 B300:B303 B298 B226:B236 B277:B278 B269 B362:B1048563 B271:B272 B275">
+  <conditionalFormatting sqref="B1:B32 B44 B98 B310 B39:B40 B49 B46:B47 B36:B37 B165 B279 B179 B89 B148:B153 B100:B101 B337:B340 B323 B266:B268 B247:B254 B187:B194 B203 B83 B167:B170 B160:B163 B77:B81 B156:B157 B85:B86 B385:B1048576 B214 B51:B74 B286 B294:B295 B243:B245 B292 B288:B289 B208:B211 B315 B317:B320 B231:B234 B216:B227 B332 B347 B326:B327 B329:B330 B236:B238 B272 B302:B307 B282:B284 B106 B141:B143 B108 B110:B138">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/template/机组花名册.xlsx
+++ b/public/template/机组花名册.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="405">
   <si>
     <t>员工号</t>
   </si>
@@ -191,6 +191,15 @@
     <t>孔繁平</t>
   </si>
   <si>
+    <t>王峰</t>
+  </si>
+  <si>
+    <t>李东</t>
+  </si>
+  <si>
+    <t>周海军</t>
+  </si>
+  <si>
     <t>石桂平</t>
   </si>
   <si>
@@ -236,9 +245,6 @@
     <t>季韬</t>
   </si>
   <si>
-    <t>王峰</t>
-  </si>
-  <si>
     <t>单国强</t>
   </si>
   <si>
@@ -263,9 +269,6 @@
     <t>唐龙</t>
   </si>
   <si>
-    <t>周海军</t>
-  </si>
-  <si>
     <t>高炜</t>
   </si>
   <si>
@@ -287,9 +290,6 @@
     <t>曹顺强</t>
   </si>
   <si>
-    <t>李东</t>
-  </si>
-  <si>
     <t>宾恩辉</t>
   </si>
   <si>
@@ -389,6 +389,9 @@
     <t>朱嘉俊</t>
   </si>
   <si>
+    <t>卢晋勋</t>
+  </si>
+  <si>
     <t>陶炼</t>
   </si>
   <si>
@@ -413,9 +416,6 @@
     <t>李旭波</t>
   </si>
   <si>
-    <t>卢晋勋</t>
-  </si>
-  <si>
     <t>张长伟</t>
   </si>
   <si>
@@ -548,138 +548,138 @@
     <t>李灿</t>
   </si>
   <si>
+    <t>李晓波</t>
+  </si>
+  <si>
+    <t>赵亚伟</t>
+  </si>
+  <si>
+    <t>王家骝</t>
+  </si>
+  <si>
+    <t>陆飞</t>
+  </si>
+  <si>
+    <t>余俊</t>
+  </si>
+  <si>
+    <t>李征征</t>
+  </si>
+  <si>
+    <t>张展鹏</t>
+  </si>
+  <si>
+    <t>孙筱鉴</t>
+  </si>
+  <si>
     <t>赵子超</t>
   </si>
   <si>
     <t>777:B类机长</t>
   </si>
   <si>
+    <t>田先进</t>
+  </si>
+  <si>
+    <t>朱皓</t>
+  </si>
+  <si>
+    <t>张丹魁</t>
+  </si>
+  <si>
+    <t>刘桢良</t>
+  </si>
+  <si>
+    <t>钱少龙</t>
+  </si>
+  <si>
+    <t>张竞怡</t>
+  </si>
+  <si>
+    <t>郭春阳</t>
+  </si>
+  <si>
+    <t>张寒义</t>
+  </si>
+  <si>
+    <t>唐浩林</t>
+  </si>
+  <si>
+    <t>韩龙</t>
+  </si>
+  <si>
+    <t>盛况</t>
+  </si>
+  <si>
+    <t>777:Z类机长</t>
+  </si>
+  <si>
+    <t>崔玉柱</t>
+  </si>
+  <si>
+    <t>周思宁</t>
+  </si>
+  <si>
+    <t>王尧</t>
+  </si>
+  <si>
+    <t>马勇</t>
+  </si>
+  <si>
+    <t>白永亮</t>
+  </si>
+  <si>
+    <t>卢彦来</t>
+  </si>
+  <si>
+    <t>姚剑鸣</t>
+  </si>
+  <si>
+    <t>贺万强</t>
+  </si>
+  <si>
+    <t>张亚朋</t>
+  </si>
+  <si>
+    <t>安阳</t>
+  </si>
+  <si>
+    <t>武中杰</t>
+  </si>
+  <si>
+    <t>陈玺</t>
+  </si>
+  <si>
+    <t>程熊</t>
+  </si>
+  <si>
+    <t>赵晓舟</t>
+  </si>
+  <si>
+    <t>田权龙</t>
+  </si>
+  <si>
+    <t>徐海锋</t>
+  </si>
+  <si>
+    <t>覃文添</t>
+  </si>
+  <si>
+    <t>吴智鑫</t>
+  </si>
+  <si>
+    <t>梁振</t>
+  </si>
+  <si>
+    <t>李正江</t>
+  </si>
+  <si>
+    <t>刘宇</t>
+  </si>
+  <si>
     <t>王靖江</t>
   </si>
   <si>
-    <t>余俊</t>
-  </si>
-  <si>
-    <t>田先进</t>
-  </si>
-  <si>
-    <t>陆飞</t>
-  </si>
-  <si>
-    <t>张展鹏</t>
-  </si>
-  <si>
-    <t>王家骝</t>
-  </si>
-  <si>
-    <t>李征征</t>
-  </si>
-  <si>
-    <t>朱皓</t>
-  </si>
-  <si>
-    <t>张丹魁</t>
-  </si>
-  <si>
-    <t>刘桢良</t>
-  </si>
-  <si>
-    <t>孙筱鉴</t>
-  </si>
-  <si>
-    <t>钱少龙</t>
-  </si>
-  <si>
-    <t>张竞怡</t>
-  </si>
-  <si>
-    <t>郭春阳</t>
-  </si>
-  <si>
-    <t>张寒义</t>
-  </si>
-  <si>
-    <t>唐浩林</t>
-  </si>
-  <si>
-    <t>韩龙</t>
-  </si>
-  <si>
-    <t>777:Z类机长</t>
-  </si>
-  <si>
-    <t>盛况</t>
-  </si>
-  <si>
-    <t>崔玉柱</t>
-  </si>
-  <si>
-    <t>李晓波</t>
-  </si>
-  <si>
-    <t>周思宁</t>
-  </si>
-  <si>
-    <t>王尧</t>
-  </si>
-  <si>
-    <t>马勇</t>
-  </si>
-  <si>
-    <t>白永亮</t>
-  </si>
-  <si>
-    <t>卢彦来</t>
-  </si>
-  <si>
-    <t>姚剑鸣</t>
-  </si>
-  <si>
-    <t>贺万强</t>
-  </si>
-  <si>
-    <t>张亚朋</t>
-  </si>
-  <si>
-    <t>安阳</t>
-  </si>
-  <si>
-    <t>武中杰</t>
-  </si>
-  <si>
-    <t>陈玺</t>
-  </si>
-  <si>
-    <t>程熊</t>
-  </si>
-  <si>
-    <t>赵晓舟</t>
-  </si>
-  <si>
-    <t>田权龙</t>
-  </si>
-  <si>
-    <t>徐海锋</t>
-  </si>
-  <si>
-    <t>覃文添</t>
-  </si>
-  <si>
-    <t>吴智鑫</t>
-  </si>
-  <si>
-    <t>梁振</t>
-  </si>
-  <si>
-    <t>李正江</t>
-  </si>
-  <si>
-    <t>刘宇</t>
-  </si>
-  <si>
-    <t>赵亚伟</t>
-  </si>
-  <si>
     <t>777:E类副驾驶</t>
   </si>
   <si>
@@ -710,15 +710,18 @@
     <t>欧阳文威</t>
   </si>
   <si>
+    <t>卢元俊</t>
+  </si>
+  <si>
     <t>谢旭纬</t>
   </si>
   <si>
+    <t>沙思丞</t>
+  </si>
+  <si>
     <t>777:C类副驾驶</t>
   </si>
   <si>
-    <t>沙思丞</t>
-  </si>
-  <si>
     <t>吴振鹏</t>
   </si>
   <si>
@@ -752,9 +755,6 @@
     <t>黄俊豪</t>
   </si>
   <si>
-    <t>卢元俊</t>
-  </si>
-  <si>
     <t>刘信</t>
   </si>
   <si>
@@ -923,6 +923,24 @@
     <t>税毅</t>
   </si>
   <si>
+    <t>何鹏程</t>
+  </si>
+  <si>
+    <t>陈昭旻</t>
+  </si>
+  <si>
+    <t>陈致远</t>
+  </si>
+  <si>
+    <t>朱珉君</t>
+  </si>
+  <si>
+    <t>胡博</t>
+  </si>
+  <si>
+    <t>周琛</t>
+  </si>
+  <si>
     <t>杨帮翔</t>
   </si>
   <si>
@@ -959,36 +977,18 @@
     <t>莫帏帏</t>
   </si>
   <si>
-    <t>朱珉君</t>
-  </si>
-  <si>
     <t>胡雨辰</t>
   </si>
   <si>
-    <t>胡博</t>
-  </si>
-  <si>
     <t>杨登科</t>
   </si>
   <si>
-    <t>陈致远</t>
-  </si>
-  <si>
-    <t>何鹏程</t>
-  </si>
-  <si>
     <t>薛力文</t>
   </si>
   <si>
-    <t>周琛</t>
-  </si>
-  <si>
     <t>张小康</t>
   </si>
   <si>
-    <t>陈昭旻</t>
-  </si>
-  <si>
     <t>黄家和</t>
   </si>
   <si>
@@ -1079,48 +1079,63 @@
     <t>许哲华</t>
   </si>
   <si>
+    <t>文强</t>
+  </si>
+  <si>
+    <t>张龙龙</t>
+  </si>
+  <si>
+    <t>韩宇航</t>
+  </si>
+  <si>
+    <t>张成</t>
+  </si>
+  <si>
     <t>庞凌博</t>
   </si>
   <si>
+    <t>黄捷</t>
+  </si>
+  <si>
+    <t>钟金宏</t>
+  </si>
+  <si>
+    <t>郭勇</t>
+  </si>
+  <si>
+    <t>李嘉杰</t>
+  </si>
+  <si>
+    <t>罗建峰</t>
+  </si>
+  <si>
+    <t>谭慧明</t>
+  </si>
+  <si>
+    <t>罗浩诚</t>
+  </si>
+  <si>
+    <t>于鄢龙</t>
+  </si>
+  <si>
+    <t>闫文平</t>
+  </si>
+  <si>
     <t>777:A1类副驾驶</t>
   </si>
   <si>
-    <t>闫文平</t>
-  </si>
-  <si>
-    <t>张龙龙</t>
-  </si>
-  <si>
     <t>王熠铭</t>
   </si>
   <si>
-    <t>黄捷</t>
-  </si>
-  <si>
-    <t>李嘉杰</t>
-  </si>
-  <si>
-    <t>韩宇航</t>
-  </si>
-  <si>
     <t>周国正</t>
   </si>
   <si>
     <t>郑杰</t>
   </si>
   <si>
-    <t>张成</t>
-  </si>
-  <si>
-    <t>文强</t>
-  </si>
-  <si>
     <t>黄兴</t>
   </si>
   <si>
-    <t>钟金宏</t>
-  </si>
-  <si>
     <t>王子林</t>
   </si>
   <si>
@@ -1130,12 +1145,6 @@
     <t>张釜浩</t>
   </si>
   <si>
-    <t>谭慧明</t>
-  </si>
-  <si>
-    <t>郭勇</t>
-  </si>
-  <si>
     <t>叶科兴</t>
   </si>
   <si>
@@ -1145,15 +1154,9 @@
     <t>陈坤淋</t>
   </si>
   <si>
-    <t>罗建峰</t>
-  </si>
-  <si>
     <t>田庭</t>
   </si>
   <si>
-    <t>于鄢龙</t>
-  </si>
-  <si>
     <t>苏晓文</t>
   </si>
   <si>
@@ -1163,9 +1166,6 @@
     <t>朱慕杰</t>
   </si>
   <si>
-    <t>罗浩诚</t>
-  </si>
-  <si>
     <t>聂莘欣</t>
   </si>
   <si>
@@ -1178,30 +1178,30 @@
     <t>吕博文</t>
   </si>
   <si>
+    <t>温佳明</t>
+  </si>
+  <si>
+    <t>钱坤洋</t>
+  </si>
+  <si>
+    <t>包忠杰</t>
+  </si>
+  <si>
+    <t>贾生琨</t>
+  </si>
+  <si>
+    <t>周艺阳</t>
+  </si>
+  <si>
+    <t>杨宇轩</t>
+  </si>
+  <si>
+    <t>熊涛</t>
+  </si>
+  <si>
     <t>划转副驾驶</t>
   </si>
   <si>
-    <t>温佳明</t>
-  </si>
-  <si>
-    <t>钱坤洋</t>
-  </si>
-  <si>
-    <t>包忠杰</t>
-  </si>
-  <si>
-    <t>贾生琨</t>
-  </si>
-  <si>
-    <t>周艺阳</t>
-  </si>
-  <si>
-    <t>杨宇轩</t>
-  </si>
-  <si>
-    <t>熊涛</t>
-  </si>
-  <si>
     <t>时浩源</t>
   </si>
   <si>
@@ -1211,9 +1211,6 @@
     <t>罗一凡</t>
   </si>
   <si>
-    <t>石志远</t>
-  </si>
-  <si>
     <t>湛怀福</t>
   </si>
   <si>
@@ -1230,6 +1227,21 @@
   </si>
   <si>
     <t>划转机长</t>
+  </si>
+  <si>
+    <t>李昊轩</t>
+  </si>
+  <si>
+    <t>李劲彧</t>
+  </si>
+  <si>
+    <t>马鸿博</t>
+  </si>
+  <si>
+    <t>彭浩</t>
+  </si>
+  <si>
+    <t>任浩翔</t>
   </si>
 </sst>
 </file>
@@ -2440,7 +2452,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C384"/>
+  <dimension ref="A1:C388"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="3" width="15.6272727272727" style="1" customWidth="1"/>
@@ -2998,354 +3010,354 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="3">
-        <v>191452</v>
+        <v>210535</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C51" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="5">
+        <v>211430</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="3">
-        <v>208985</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="C52" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="3">
-        <v>206632</v>
+        <v>181783</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="3">
-        <v>199680</v>
+        <v>191452</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="3">
-        <v>181503</v>
+        <v>208985</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="3">
-        <v>181513</v>
+        <v>206632</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="3">
-        <v>181558</v>
+        <v>199680</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="3">
-        <v>181727</v>
+        <v>181503</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3">
-        <v>186662</v>
+        <v>181513</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="3">
-        <v>193391</v>
+        <v>181558</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="3">
-        <v>201906</v>
+        <v>181727</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="3">
-        <v>202990</v>
+        <v>186662</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="3">
-        <v>901768</v>
+        <v>193391</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="3">
-        <v>201982</v>
+        <v>201906</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="3">
-        <v>210535</v>
+        <v>202990</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="3">
-        <v>905175</v>
+        <v>901768</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="3">
-        <v>901449</v>
+        <v>201982</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="3">
-        <v>181798</v>
+        <v>905175</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="3">
-        <v>187952</v>
+        <v>901449</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="3">
-        <v>196520</v>
+        <v>181798</v>
       </c>
       <c r="B70" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="3">
-        <v>213485</v>
+        <v>187952</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="3">
-        <v>212801</v>
+        <v>196520</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="3">
-        <v>189182</v>
+        <v>213485</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>77</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="3">
-        <v>181783</v>
+        <v>212801</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="6">
-        <v>198207</v>
-      </c>
-      <c r="B75" s="6" t="s">
+      <c r="A75" s="3">
+        <v>189182</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="6">
-        <v>204821</v>
+        <v>198207</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>80</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="3">
-        <v>216861</v>
-      </c>
-      <c r="B77" s="4" t="s">
+      <c r="A77" s="6">
+        <v>204821</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="3">
-        <v>210252</v>
+        <v>216861</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="3">
-        <v>216502</v>
+        <v>210252</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="3">
-        <v>214335</v>
+        <v>216502</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="5">
-        <v>202368</v>
-      </c>
-      <c r="B81" s="5" t="s">
+      <c r="A81" s="3">
+        <v>214335</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="5">
-        <v>211430</v>
+        <v>202368</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -3356,7 +3368,7 @@
         <v>87</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -3367,7 +3379,7 @@
         <v>88</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -3378,7 +3390,7 @@
         <v>89</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -3389,7 +3401,7 @@
         <v>90</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -3400,7 +3412,7 @@
         <v>91</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -3411,7 +3423,7 @@
         <v>92</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -3422,7 +3434,7 @@
         <v>93</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -3433,7 +3445,7 @@
         <v>94</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -3444,7 +3456,7 @@
         <v>95</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -3455,7 +3467,7 @@
         <v>96</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -3466,7 +3478,7 @@
         <v>97</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -3477,7 +3489,7 @@
         <v>98</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -3488,7 +3500,7 @@
         <v>99</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -3499,7 +3511,7 @@
         <v>100</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -3510,7 +3522,7 @@
         <v>101</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:3">
@@ -3521,7 +3533,7 @@
         <v>102</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99" spans="1:3">
@@ -3532,7 +3544,7 @@
         <v>103</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -3543,7 +3555,7 @@
         <v>104</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -3554,7 +3566,7 @@
         <v>105</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -3565,7 +3577,7 @@
         <v>106</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -3576,7 +3588,7 @@
         <v>107</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="104" ht="42" spans="1:3">
@@ -3702,90 +3714,90 @@
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="3">
-        <v>210510</v>
+        <v>212914</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>120</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="3">
-        <v>193177</v>
+        <v>210510</v>
       </c>
       <c r="B116" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="3">
-        <v>202989</v>
+        <v>193177</v>
       </c>
       <c r="B117" s="4" t="s">
         <v>123</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="3">
-        <v>208984</v>
+        <v>202989</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>124</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="3">
-        <v>212810</v>
+        <v>208984</v>
       </c>
       <c r="B119" s="4" t="s">
         <v>125</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="3">
-        <v>184767</v>
+        <v>212810</v>
       </c>
       <c r="B120" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="3">
-        <v>193238</v>
+        <v>184767</v>
       </c>
       <c r="B121" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="3">
-        <v>212914</v>
+        <v>193238</v>
       </c>
       <c r="B122" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -3796,7 +3808,7 @@
         <v>129</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -3807,7 +3819,7 @@
         <v>130</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -3818,7 +3830,7 @@
         <v>131</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -3829,7 +3841,7 @@
         <v>132</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -3840,7 +3852,7 @@
         <v>133</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -3851,7 +3863,7 @@
         <v>134</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -3862,7 +3874,7 @@
         <v>135</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="130" spans="1:3">
@@ -3873,7 +3885,7 @@
         <v>136</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="131" spans="1:3">
@@ -3884,7 +3896,7 @@
         <v>137</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -3895,7 +3907,7 @@
         <v>138</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -3906,7 +3918,7 @@
         <v>139</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -3917,7 +3929,7 @@
         <v>140</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -3928,7 +3940,7 @@
         <v>141</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -3939,7 +3951,7 @@
         <v>142</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -3950,7 +3962,7 @@
         <v>143</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="138" spans="1:3">
@@ -3961,7 +3973,7 @@
         <v>144</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -3972,7 +3984,7 @@
         <v>145</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="140" spans="1:3">
@@ -3983,7 +3995,7 @@
         <v>146</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="141" spans="1:3">
@@ -3994,7 +4006,7 @@
         <v>147</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="142" spans="1:3">
@@ -4005,7 +4017,7 @@
         <v>148</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="143" spans="1:3">
@@ -4016,7 +4028,7 @@
         <v>149</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="144" spans="1:3">
@@ -4027,7 +4039,7 @@
         <v>150</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="145" ht="42" spans="1:3">
@@ -4038,7 +4050,7 @@
         <v>151</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="146" spans="1:3">
@@ -4049,7 +4061,7 @@
         <v>152</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="147" spans="1:3">
@@ -4060,7 +4072,7 @@
         <v>153</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="148" spans="1:3">
@@ -4071,7 +4083,7 @@
         <v>154</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="149" spans="1:3">
@@ -4082,7 +4094,7 @@
         <v>155</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="150" spans="1:3">
@@ -4093,7 +4105,7 @@
         <v>156</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="151" spans="1:3">
@@ -4104,7 +4116,7 @@
         <v>157</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -4115,7 +4127,7 @@
         <v>158</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -4126,7 +4138,7 @@
         <v>159</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="154" ht="28" spans="1:3">
@@ -4137,7 +4149,7 @@
         <v>160</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -4148,7 +4160,7 @@
         <v>161</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -4159,7 +4171,7 @@
         <v>162</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -4170,7 +4182,7 @@
         <v>163</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="158" spans="1:3">
@@ -4181,7 +4193,7 @@
         <v>164</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -4192,7 +4204,7 @@
         <v>165</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="160" spans="1:3">
@@ -4203,7 +4215,7 @@
         <v>166</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="161" spans="1:3">
@@ -4214,7 +4226,7 @@
         <v>167</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="162" spans="1:3">
@@ -4225,7 +4237,7 @@
         <v>168</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="163" spans="1:3">
@@ -4236,7 +4248,7 @@
         <v>169</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="164" spans="1:3">
@@ -4247,7 +4259,7 @@
         <v>170</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -4258,7 +4270,7 @@
         <v>171</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -4269,238 +4281,238 @@
         <v>172</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167" s="3">
-        <v>188592</v>
+        <v>205130</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>173</v>
       </c>
       <c r="C167" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="3">
+        <v>202379</v>
+      </c>
+      <c r="B168" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="168" spans="1:3">
-      <c r="A168" s="4">
-        <v>211937</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="C168" s="4" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169" s="3">
-        <v>208107</v>
+        <v>905161</v>
       </c>
       <c r="B169" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="3">
+        <v>903942</v>
+      </c>
+      <c r="B170" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C169" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" s="4">
-        <v>210767</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>177</v>
-      </c>
       <c r="C170" s="4" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171" s="3">
-        <v>903942</v>
+        <v>208107</v>
       </c>
       <c r="B171" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" s="6">
+        <v>192993</v>
+      </c>
+      <c r="B172" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C171" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" s="3">
-        <v>189186</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="C172" s="4" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173" s="3">
-        <v>905161</v>
+        <v>189186</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174" s="6">
-        <v>192993</v>
+        <v>904950</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>174</v>
+        <v>122</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175" s="3">
-        <v>210155</v>
+        <v>188592</v>
       </c>
       <c r="B175" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C175" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C175" s="4" t="s">
-        <v>174</v>
-      </c>
     </row>
     <row r="176" spans="1:3">
-      <c r="A176" s="3">
-        <v>901756</v>
+      <c r="A176" s="4">
+        <v>210767</v>
       </c>
       <c r="B176" s="4" t="s">
         <v>183</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177" s="3">
-        <v>901557</v>
+        <v>210155</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>184</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="178" spans="1:3">
-      <c r="A178" s="6">
-        <v>904950</v>
-      </c>
-      <c r="B178" s="7" t="s">
+      <c r="A178" s="3">
+        <v>901756</v>
+      </c>
+      <c r="B178" s="4" t="s">
         <v>185</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="179" spans="1:3">
-      <c r="A179" s="4">
-        <v>210625</v>
+      <c r="A179" s="3">
+        <v>901557</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>186</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" spans="1:3">
-      <c r="A180" s="3">
-        <v>215073</v>
+      <c r="A180" s="4">
+        <v>210625</v>
       </c>
       <c r="B180" s="4" t="s">
         <v>187</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="181" spans="1:3">
-      <c r="A181" s="5">
+      <c r="A181" s="3">
+        <v>215073</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="5">
         <v>184790</v>
       </c>
-      <c r="B181" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
-      <c r="A182" s="3">
+      <c r="B182" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" s="3">
         <v>219807</v>
       </c>
-      <c r="B182" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183" s="6">
+      <c r="B183" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" s="6">
         <v>211588</v>
       </c>
-      <c r="B183" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
-      <c r="A184" s="3">
-        <v>214908</v>
-      </c>
-      <c r="B184" s="4" t="s">
+      <c r="B184" s="7" t="s">
         <v>191</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185" s="3">
-        <v>211318</v>
+        <v>214908</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186" s="3">
-        <v>210787</v>
+        <v>211318</v>
       </c>
       <c r="B186" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C186" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187" s="3">
-        <v>205130</v>
+        <v>210787</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>195</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -4511,7 +4523,7 @@
         <v>196</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -4522,7 +4534,7 @@
         <v>197</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -4533,7 +4545,7 @@
         <v>198</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -4544,7 +4556,7 @@
         <v>199</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -4555,7 +4567,7 @@
         <v>200</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -4566,7 +4578,7 @@
         <v>201</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -4577,7 +4589,7 @@
         <v>202</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -4588,7 +4600,7 @@
         <v>203</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -4599,7 +4611,7 @@
         <v>204</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -4610,7 +4622,7 @@
         <v>205</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -4621,7 +4633,7 @@
         <v>206</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -4632,7 +4644,7 @@
         <v>207</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -4643,7 +4655,7 @@
         <v>208</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -4654,7 +4666,7 @@
         <v>209</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -4665,7 +4677,7 @@
         <v>210</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -4676,7 +4688,7 @@
         <v>211</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -4687,7 +4699,7 @@
         <v>212</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -4698,7 +4710,7 @@
         <v>213</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -4709,7 +4721,7 @@
         <v>214</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -4720,12 +4732,12 @@
         <v>215</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="208" spans="1:3">
-      <c r="A208" s="3">
-        <v>202379</v>
+      <c r="A208" s="4">
+        <v>211937</v>
       </c>
       <c r="B208" s="4" t="s">
         <v>216</v>
@@ -4824,156 +4836,156 @@
     </row>
     <row r="217" spans="1:3">
       <c r="A217" s="3">
-        <v>230397</v>
+        <v>247704</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>227</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218" s="3">
-        <v>248322</v>
+        <v>230397</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219" s="3">
-        <v>248319</v>
+        <v>248322</v>
       </c>
       <c r="B219" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C219" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220" s="3">
-        <v>258463</v>
+        <v>248319</v>
       </c>
       <c r="B220" s="4" t="s">
         <v>231</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221" s="3">
-        <v>261764</v>
+        <v>258463</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>232</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" s="3">
-        <v>262062</v>
+        <v>261764</v>
       </c>
       <c r="B222" s="4" t="s">
         <v>233</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223" s="3">
-        <v>265806</v>
+        <v>262062</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>234</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224" s="3">
-        <v>265801</v>
+        <v>265806</v>
       </c>
       <c r="B224" s="4" t="s">
         <v>235</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="225" spans="1:3">
-      <c r="A225" s="6">
+      <c r="A225" s="3">
+        <v>265801</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" s="6">
         <v>210590</v>
       </c>
-      <c r="B225" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
-      <c r="A226" s="3">
-        <v>257603</v>
-      </c>
-      <c r="B226" s="4" t="s">
+      <c r="B226" s="6" t="s">
         <v>237</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227" s="3">
-        <v>253772</v>
+        <v>257603</v>
       </c>
       <c r="B227" s="4" t="s">
         <v>238</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228" s="3">
-        <v>259803</v>
+        <v>253772</v>
       </c>
       <c r="B228" s="4" t="s">
         <v>239</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229" s="3">
-        <v>263416</v>
+        <v>259803</v>
       </c>
       <c r="B229" s="4" t="s">
         <v>240</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230" s="3">
-        <v>247704</v>
+        <v>263416</v>
       </c>
       <c r="B230" s="4" t="s">
         <v>241</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -4984,7 +4996,7 @@
         <v>242</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -4995,7 +5007,7 @@
         <v>243</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -5006,7 +5018,7 @@
         <v>244</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -5017,7 +5029,7 @@
         <v>245</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -5028,7 +5040,7 @@
         <v>246</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -5039,7 +5051,7 @@
         <v>247</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -5050,7 +5062,7 @@
         <v>248</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="238" spans="1:3">
@@ -5061,7 +5073,7 @@
         <v>249</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="239" spans="1:3">
@@ -5072,7 +5084,7 @@
         <v>250</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -5083,7 +5095,7 @@
         <v>251</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="241" spans="1:3">
@@ -5094,7 +5106,7 @@
         <v>252</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -5105,7 +5117,7 @@
         <v>253</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -5116,7 +5128,7 @@
         <v>254</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -5127,7 +5139,7 @@
         <v>255</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -5138,7 +5150,7 @@
         <v>256</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -5149,7 +5161,7 @@
         <v>257</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -5582,234 +5594,234 @@
       </c>
     </row>
     <row r="286" spans="1:3">
-      <c r="A286" s="3">
-        <v>213858</v>
+      <c r="A286" s="4">
+        <v>236145</v>
       </c>
       <c r="B286" s="4" t="s">
         <v>298</v>
       </c>
       <c r="C286" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" s="5">
+        <v>274985</v>
+      </c>
+      <c r="B287" s="5" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="287" spans="1:3">
-      <c r="A287" s="3">
+      <c r="C287" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" s="6">
+        <v>279543</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C288" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289" s="3">
+        <v>270788</v>
+      </c>
+      <c r="B289" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C289" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290" s="4">
+        <v>285783</v>
+      </c>
+      <c r="B290" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="C290" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291" s="5">
+        <v>275099</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C291" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292" s="3">
+        <v>213858</v>
+      </c>
+      <c r="B292" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C292" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293" s="3">
         <v>268097</v>
       </c>
-      <c r="B287" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C287" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3">
-      <c r="A288" s="4">
+      <c r="B293" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C293" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294" s="4">
         <v>276385</v>
-      </c>
-      <c r="B288" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="C288" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3">
-      <c r="A289" s="4">
-        <v>281970</v>
-      </c>
-      <c r="B289" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C289" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3">
-      <c r="A290" s="3">
-        <v>263409</v>
-      </c>
-      <c r="B290" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="C290" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3">
-      <c r="A291" s="4">
-        <v>210531</v>
-      </c>
-      <c r="B291" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C291" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3">
-      <c r="A292" s="4">
-        <v>276019</v>
-      </c>
-      <c r="B292" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="C292" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
-      <c r="A293" s="6">
-        <v>272827</v>
-      </c>
-      <c r="B293" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="C293" s="4" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3">
-      <c r="A294" s="3">
-        <v>279043</v>
       </c>
       <c r="B294" s="4" t="s">
         <v>307</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="3">
-        <v>246465</v>
+      <c r="A295" s="4">
+        <v>281970</v>
       </c>
       <c r="B295" s="4" t="s">
         <v>308</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="296" spans="1:3">
-      <c r="A296" s="4">
-        <v>261778</v>
+      <c r="A296" s="3">
+        <v>263409</v>
       </c>
       <c r="B296" s="4" t="s">
         <v>309</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="297" spans="1:3">
-      <c r="A297" s="3">
-        <v>270788</v>
+      <c r="A297" s="4">
+        <v>210531</v>
       </c>
       <c r="B297" s="4" t="s">
         <v>310</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="298" spans="1:3">
-      <c r="A298" s="3">
-        <v>289953</v>
+      <c r="A298" s="4">
+        <v>276019</v>
       </c>
       <c r="B298" s="4" t="s">
         <v>311</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="299" spans="1:3">
-      <c r="A299" s="4">
-        <v>285783</v>
-      </c>
-      <c r="B299" s="4" t="s">
+      <c r="A299" s="6">
+        <v>272827</v>
+      </c>
+      <c r="B299" s="6" t="s">
         <v>312</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="300" spans="1:3">
-      <c r="A300" s="6">
-        <v>284122</v>
-      </c>
-      <c r="B300" s="6" t="s">
+      <c r="A300" s="3">
+        <v>279043</v>
+      </c>
+      <c r="B300" s="4" t="s">
         <v>313</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="6">
-        <v>279543</v>
-      </c>
-      <c r="B301" s="6" t="s">
+      <c r="A301" s="3">
+        <v>246465</v>
+      </c>
+      <c r="B301" s="4" t="s">
         <v>314</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" s="4">
-        <v>236145</v>
+        <v>261778</v>
       </c>
       <c r="B302" s="4" t="s">
         <v>315</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="4">
-        <v>264064</v>
+      <c r="A303" s="3">
+        <v>289953</v>
       </c>
       <c r="B303" s="4" t="s">
         <v>316</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="304" spans="1:3">
-      <c r="A304" s="5">
-        <v>275099</v>
-      </c>
-      <c r="B304" s="5" t="s">
+      <c r="A304" s="6">
+        <v>284122</v>
+      </c>
+      <c r="B304" s="6" t="s">
         <v>317</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="305" spans="1:3">
-      <c r="A305" s="5">
-        <v>282654</v>
-      </c>
-      <c r="B305" s="5" t="s">
+      <c r="A305" s="4">
+        <v>264064</v>
+      </c>
+      <c r="B305" s="4" t="s">
         <v>318</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="306" spans="1:3">
       <c r="A306" s="5">
-        <v>274985</v>
+        <v>282654</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>319</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="307" spans="1:3">
@@ -5820,7 +5832,7 @@
         <v>320</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="1:3">
@@ -5831,7 +5843,7 @@
         <v>321</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -5842,7 +5854,7 @@
         <v>322</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -5853,7 +5865,7 @@
         <v>323</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="311" spans="1:3">
@@ -5864,7 +5876,7 @@
         <v>324</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="312" spans="1:3">
@@ -5875,7 +5887,7 @@
         <v>325</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="313" spans="1:3">
@@ -5886,7 +5898,7 @@
         <v>326</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="314" spans="1:3">
@@ -5897,7 +5909,7 @@
         <v>327</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="315" spans="1:3">
@@ -5908,7 +5920,7 @@
         <v>328</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="316" spans="1:3">
@@ -5919,7 +5931,7 @@
         <v>329</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="317" spans="1:3">
@@ -5930,7 +5942,7 @@
         <v>330</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="318" spans="1:3">
@@ -5941,7 +5953,7 @@
         <v>331</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="319" spans="1:3">
@@ -5952,7 +5964,7 @@
         <v>332</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="320" spans="1:3">
@@ -5963,7 +5975,7 @@
         <v>333</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="321" spans="1:3">
@@ -5974,7 +5986,7 @@
         <v>334</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="322" spans="1:3">
@@ -5985,7 +5997,7 @@
         <v>335</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="323" spans="1:3">
@@ -5996,7 +6008,7 @@
         <v>336</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="324" spans="1:3">
@@ -6007,7 +6019,7 @@
         <v>337</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="325" spans="1:3">
@@ -6018,7 +6030,7 @@
         <v>338</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="326" spans="1:3">
@@ -6029,7 +6041,7 @@
         <v>339</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="327" spans="1:3">
@@ -6040,7 +6052,7 @@
         <v>340</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="328" spans="1:3">
@@ -6051,7 +6063,7 @@
         <v>341</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="329" spans="1:3">
@@ -6062,7 +6074,7 @@
         <v>342</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -6073,7 +6085,7 @@
         <v>343</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -6084,7 +6096,7 @@
         <v>344</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="332" spans="1:3">
@@ -6095,7 +6107,7 @@
         <v>345</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="333" spans="1:3">
@@ -6106,7 +6118,7 @@
         <v>346</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="334" spans="1:3">
@@ -6117,7 +6129,7 @@
         <v>347</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="335" spans="1:3">
@@ -6128,7 +6140,7 @@
         <v>348</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="336" spans="1:3">
@@ -6139,315 +6151,315 @@
         <v>349</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="337" spans="1:3">
-      <c r="A337" s="3">
-        <v>284330</v>
-      </c>
-      <c r="B337" s="4" t="s">
+      <c r="A337" s="6">
+        <v>273305</v>
+      </c>
+      <c r="B337" s="7" t="s">
         <v>350</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
     </row>
     <row r="338" spans="1:3">
       <c r="A338" s="3">
-        <v>284331</v>
+        <v>284332</v>
       </c>
       <c r="B338" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" s="6">
+        <v>281004</v>
+      </c>
+      <c r="B339" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="C338" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3">
-      <c r="A339" s="3">
-        <v>284332</v>
-      </c>
-      <c r="B339" s="4" t="s">
+      <c r="C339" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" s="6">
+        <v>271929</v>
+      </c>
+      <c r="B340" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="C339" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3">
-      <c r="A340" s="3">
-        <v>291033</v>
-      </c>
-      <c r="B340" s="4" t="s">
+      <c r="C340" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" s="3">
+        <v>284330</v>
+      </c>
+      <c r="B341" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="C340" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3">
-      <c r="A341" s="5">
+      <c r="C341" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" s="5">
         <v>288902</v>
       </c>
-      <c r="B341" s="5" t="s">
+      <c r="B342" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="C341" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3">
-      <c r="A342" s="6">
-        <v>292765</v>
-      </c>
-      <c r="B342" s="7" t="s">
-        <v>356</v>
-      </c>
       <c r="C342" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
     </row>
     <row r="343" spans="1:3">
       <c r="A343" s="6">
-        <v>281004</v>
+        <v>278746</v>
       </c>
       <c r="B343" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
     </row>
     <row r="344" spans="1:3">
       <c r="A344" s="6">
-        <v>278747</v>
+        <v>283833</v>
       </c>
       <c r="B344" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
     </row>
     <row r="345" spans="1:3">
       <c r="A345" s="6">
-        <v>263420</v>
+        <v>292765</v>
       </c>
       <c r="B345" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
     </row>
     <row r="346" spans="1:3">
       <c r="A346" s="6">
-        <v>271929</v>
+        <v>294086</v>
       </c>
       <c r="B346" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
     </row>
     <row r="347" spans="1:3">
       <c r="A347" s="6">
-        <v>273305</v>
+        <v>280950</v>
       </c>
       <c r="B347" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
     </row>
     <row r="348" spans="1:3">
       <c r="A348" s="6">
-        <v>280074</v>
+        <v>273284</v>
       </c>
       <c r="B348" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
     </row>
     <row r="349" spans="1:3">
       <c r="A349" s="6">
-        <v>278746</v>
+        <v>297287</v>
       </c>
       <c r="B349" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" s="3">
+        <v>284331</v>
+      </c>
+      <c r="B350" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="C349" s="4" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3">
-      <c r="A350" s="6">
-        <v>284201</v>
-      </c>
-      <c r="B350" s="7" t="s">
+      <c r="C350" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C350" s="4" t="s">
-        <v>351</v>
-      </c>
     </row>
     <row r="351" spans="1:3">
-      <c r="A351" s="6">
-        <v>276712</v>
-      </c>
-      <c r="B351" s="7" t="s">
+      <c r="A351" s="3">
+        <v>291033</v>
+      </c>
+      <c r="B351" s="4" t="s">
         <v>365</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="352" spans="1:3">
       <c r="A352" s="6">
-        <v>280145</v>
+        <v>278747</v>
       </c>
       <c r="B352" s="7" t="s">
         <v>366</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" s="6">
-        <v>280950</v>
+        <v>263420</v>
       </c>
       <c r="B353" s="7" t="s">
         <v>367</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="354" spans="1:3">
       <c r="A354" s="6">
-        <v>283833</v>
+        <v>280074</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>368</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="355" spans="1:3">
       <c r="A355" s="6">
-        <v>294947</v>
+        <v>284201</v>
       </c>
       <c r="B355" s="7" t="s">
         <v>369</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="356" spans="1:3">
       <c r="A356" s="6">
-        <v>282686</v>
+        <v>276712</v>
       </c>
       <c r="B356" s="7" t="s">
         <v>370</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="357" spans="1:3">
       <c r="A357" s="6">
-        <v>282119</v>
+        <v>280145</v>
       </c>
       <c r="B357" s="7" t="s">
         <v>371</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="358" spans="1:3">
       <c r="A358" s="6">
-        <v>294086</v>
+        <v>294947</v>
       </c>
       <c r="B358" s="7" t="s">
         <v>372</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" s="6">
-        <v>298124</v>
+        <v>282686</v>
       </c>
       <c r="B359" s="7" t="s">
         <v>373</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="360" spans="1:3">
       <c r="A360" s="6">
-        <v>297287</v>
+        <v>282119</v>
       </c>
       <c r="B360" s="7" t="s">
         <v>374</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="361" spans="1:3">
       <c r="A361" s="6">
-        <v>297292</v>
+        <v>298124</v>
       </c>
       <c r="B361" s="7" t="s">
         <v>375</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="6">
-        <v>294511</v>
+        <v>297292</v>
       </c>
       <c r="B362" s="7" t="s">
         <v>376</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="363" spans="1:3">
       <c r="A363" s="6">
-        <v>298146</v>
+        <v>294511</v>
       </c>
       <c r="B363" s="7" t="s">
         <v>377</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="364" spans="1:3">
       <c r="A364" s="6">
-        <v>273284</v>
+        <v>298146</v>
       </c>
       <c r="B364" s="7" t="s">
         <v>378</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -6458,7 +6470,7 @@
         <v>379</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -6469,7 +6481,7 @@
         <v>380</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -6480,7 +6492,7 @@
         <v>381</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -6491,7 +6503,7 @@
         <v>382</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
     </row>
     <row r="369" spans="1:3">
@@ -6499,10 +6511,10 @@
         <v>268080</v>
       </c>
       <c r="B369" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
     </row>
     <row r="370" spans="1:3">
@@ -6510,10 +6522,10 @@
         <v>906064</v>
       </c>
       <c r="B370" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
     </row>
     <row r="371" spans="1:3">
@@ -6521,10 +6533,10 @@
         <v>283744</v>
       </c>
       <c r="B371" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
     </row>
     <row r="372" spans="1:3">
@@ -6532,10 +6544,10 @@
         <v>286107</v>
       </c>
       <c r="B372" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
     </row>
     <row r="373" spans="1:3">
@@ -6543,10 +6555,10 @@
         <v>288732</v>
       </c>
       <c r="B373" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
     </row>
     <row r="374" spans="1:3">
@@ -6554,10 +6566,10 @@
         <v>289565</v>
       </c>
       <c r="B374" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
     </row>
     <row r="375" spans="1:3">
@@ -6565,10 +6577,10 @@
         <v>294936</v>
       </c>
       <c r="B375" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C375" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="C375" s="4" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="376" spans="1:3">
@@ -6579,7 +6591,7 @@
         <v>391</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="377" spans="1:3">
@@ -6590,7 +6602,7 @@
         <v>392</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="378" spans="1:3">
@@ -6601,77 +6613,121 @@
         <v>393</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" s="6">
-        <v>303204</v>
+        <v>302251</v>
       </c>
       <c r="B379" s="7" t="s">
         <v>394</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" s="6">
-        <v>302251</v>
+        <v>302252</v>
       </c>
       <c r="B380" s="7" t="s">
         <v>395</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="381" spans="1:3">
       <c r="A381" s="6">
-        <v>302252</v>
+        <v>303944</v>
       </c>
       <c r="B381" s="7" t="s">
         <v>396</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="382" spans="1:3">
       <c r="A382" s="6">
-        <v>303944</v>
+        <v>302249</v>
       </c>
       <c r="B382" s="7" t="s">
         <v>397</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="383" spans="1:3">
       <c r="A383" s="6">
-        <v>302249</v>
+        <v>326411</v>
       </c>
       <c r="B383" s="7" t="s">
         <v>398</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
     </row>
     <row r="384" spans="1:3">
       <c r="A384" s="6">
-        <v>326411</v>
+        <v>284925</v>
       </c>
       <c r="B384" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>400</v>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385" s="6">
+        <v>290948</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3">
+      <c r="A386" s="6">
+        <v>291329</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3">
+      <c r="A387" s="6">
+        <v>281973</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388" s="6">
+        <v>275017</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B32 B44 B98 B310 B39:B40 B49 B46:B47 B36:B37 B165 B279 B179 B89 B148:B153 B100:B101 B337:B340 B323 B266:B268 B247:B254 B187:B194 B203 B83 B167:B170 B160:B163 B77:B81 B156:B157 B85:B86 B385:B1048576 B214 B51:B74 B286 B294:B295 B243:B245 B292 B288:B289 B208:B211 B315 B317:B320 B231:B234 B216:B227 B332 B347 B326:B327 B329:B330 B236:B238 B272 B302:B307 B282:B284 B106 B141:B143 B108 B110:B138">
+  <conditionalFormatting sqref="B1:B32 B44 B98 B310 B39:B40 B49 B46:B47 B36:B37 B165 B279 B167:B168 B188:B194 B291:B292 B89 B148:B153 B100:B101 B110:B138 B171 B350:B351 B315 B141:B143 B208:B211 B323 B266:B268 B247:B254 B326:B327 B282:B284 B108 B78:B83 B231:B234 B329:B330 B305:B307 B236:B238 B218:B228 B341 B389:B1048576 B160:B163 B180 B156:B157 B85:B86 B106 B286:B287 B216 B337:B338 B214 B53:B75 B51 B317:B320 B203 B332 B272 B243:B245 B300:B301 B298 B294:B295 B175:B176">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/template/机组花名册.xlsx
+++ b/public/template/机组花名册.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11630"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="435">
   <si>
     <t>员工号</t>
   </si>
@@ -584,6 +584,9 @@
     <t>张展鹏</t>
   </si>
   <si>
+    <t>孙筱鉴</t>
+  </si>
+  <si>
     <t>赵子超</t>
   </si>
   <si>
@@ -602,9 +605,6 @@
     <t>刘桢良</t>
   </si>
   <si>
-    <t>孙筱鉴</t>
-  </si>
-  <si>
     <t>钱少龙</t>
   </si>
   <si>
@@ -731,6 +731,9 @@
     <t>谢旭纬</t>
   </si>
   <si>
+    <t>黄俊豪</t>
+  </si>
+  <si>
     <t>沙思丞</t>
   </si>
   <si>
@@ -767,9 +770,6 @@
     <t>任泽尧</t>
   </si>
   <si>
-    <t>黄俊豪</t>
-  </si>
-  <si>
     <t>刘信</t>
   </si>
   <si>
@@ -818,6 +818,12 @@
     <t>田凯文</t>
   </si>
   <si>
+    <t>袁皓华</t>
+  </si>
+  <si>
+    <t>张义涛</t>
+  </si>
+  <si>
     <t>陈兆铭</t>
   </si>
   <si>
@@ -857,9 +863,6 @@
     <t>车有路</t>
   </si>
   <si>
-    <t>张义涛</t>
-  </si>
-  <si>
     <t>邓汉昕</t>
   </si>
   <si>
@@ -893,9 +896,6 @@
     <t>黄磊</t>
   </si>
   <si>
-    <t>袁皓华</t>
-  </si>
-  <si>
     <t>章辉</t>
   </si>
   <si>
@@ -953,6 +953,21 @@
     <t>胡博</t>
   </si>
   <si>
+    <t>周琛</t>
+  </si>
+  <si>
+    <t>蓝锦坚</t>
+  </si>
+  <si>
+    <t>华显涛</t>
+  </si>
+  <si>
+    <t>黄家和</t>
+  </si>
+  <si>
+    <t>朱灿仪</t>
+  </si>
+  <si>
     <t>杨帮翔</t>
   </si>
   <si>
@@ -962,9 +977,6 @@
     <t>刘镇毓</t>
   </si>
   <si>
-    <t>华显涛</t>
-  </si>
-  <si>
     <t>任文煜</t>
   </si>
   <si>
@@ -998,30 +1010,18 @@
     <t>薛力文</t>
   </si>
   <si>
-    <t>周琛</t>
-  </si>
-  <si>
     <t>张小康</t>
   </si>
   <si>
-    <t>黄家和</t>
-  </si>
-  <si>
     <t>唐选尧</t>
   </si>
   <si>
-    <t>朱灿仪</t>
-  </si>
-  <si>
     <t>曹旭泉</t>
   </si>
   <si>
     <t>林锦源</t>
   </si>
   <si>
-    <t>蓝锦坚</t>
-  </si>
-  <si>
     <t>马天浩</t>
   </si>
   <si>
@@ -1257,6 +1257,81 @@
   </si>
   <si>
     <t>任浩翔</t>
+  </si>
+  <si>
+    <t>905172</t>
+  </si>
+  <si>
+    <t>唐杰斌</t>
+  </si>
+  <si>
+    <t>张家豪</t>
+  </si>
+  <si>
+    <t>刘瀚阳</t>
+  </si>
+  <si>
+    <t>张一帆</t>
+  </si>
+  <si>
+    <t>杜雨恒</t>
+  </si>
+  <si>
+    <t>胡安杰</t>
+  </si>
+  <si>
+    <t>季望能</t>
+  </si>
+  <si>
+    <t>朱春期</t>
+  </si>
+  <si>
+    <t>杨奇明</t>
+  </si>
+  <si>
+    <t>颜文彬</t>
+  </si>
+  <si>
+    <t>谢先正</t>
+  </si>
+  <si>
+    <t>姚望</t>
+  </si>
+  <si>
+    <t>汪杨</t>
+  </si>
+  <si>
+    <t>刘瑞奇</t>
+  </si>
+  <si>
+    <t>刘丹</t>
+  </si>
+  <si>
+    <t>丁宇</t>
+  </si>
+  <si>
+    <t>周号</t>
+  </si>
+  <si>
+    <t>马崇</t>
+  </si>
+  <si>
+    <t>张得喜</t>
+  </si>
+  <si>
+    <t>刘晋鹏</t>
+  </si>
+  <si>
+    <t>尤致衡</t>
+  </si>
+  <si>
+    <t>惠晓飞</t>
+  </si>
+  <si>
+    <t>邓超</t>
+  </si>
+  <si>
+    <t>熊鑫</t>
   </si>
 </sst>
 </file>
@@ -2488,7 +2563,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D388"/>
+  <dimension ref="A1:D412"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="15.6272727272727" style="1" customWidth="1"/>
@@ -4919,87 +4994,87 @@
       </c>
     </row>
     <row r="174" spans="1:4">
-      <c r="A174" s="5">
+      <c r="A174" s="9">
+        <v>904950</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="5">
         <v>188592</v>
       </c>
-      <c r="B174" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C174" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D174" s="6" t="s">
+      <c r="B175" s="6" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="175" spans="1:4">
-      <c r="A175" s="6">
+      <c r="C175" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="6">
         <v>210767</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C175" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4">
-      <c r="A176" s="5">
-        <v>210155</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>188</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="5">
-        <v>901756</v>
+        <v>210155</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>189</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="5">
-        <v>901557</v>
+        <v>901756</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>190</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="9">
-        <v>904950</v>
-      </c>
-      <c r="B179" s="10" t="s">
+      <c r="A179" s="5">
+        <v>901557</v>
+      </c>
+      <c r="B179" s="6" t="s">
         <v>191</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5013,7 +5088,7 @@
         <v>13</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5027,7 +5102,7 @@
         <v>10</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5041,7 +5116,7 @@
         <v>8</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5055,7 +5130,7 @@
         <v>10</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5069,7 +5144,7 @@
         <v>8</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5083,7 +5158,7 @@
         <v>8</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5550,7 +5625,7 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="5">
-        <v>248322</v>
+        <v>263416</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>234</v>
@@ -5559,68 +5634,68 @@
         <v>5</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="5">
-        <v>248319</v>
+        <v>248322</v>
       </c>
       <c r="B220" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D220" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="C220" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D220" s="6" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="5">
-        <v>258463</v>
+        <v>248319</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>237</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="5">
-        <v>261764</v>
+        <v>258463</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>238</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="5">
-        <v>262062</v>
+        <v>261764</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>239</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="5">
-        <v>265806</v>
+        <v>262062</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>240</v>
@@ -5629,68 +5704,68 @@
         <v>13</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="5">
-        <v>265801</v>
+        <v>265806</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>241</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="226" spans="1:4">
-      <c r="A226" s="9">
+      <c r="A226" s="5">
+        <v>265801</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="9">
         <v>210590</v>
       </c>
-      <c r="B226" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="C226" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D226" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4">
-      <c r="A227" s="5">
-        <v>257603</v>
-      </c>
-      <c r="B227" s="6" t="s">
+      <c r="B227" s="9" t="s">
         <v>243</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="5">
-        <v>253772</v>
+        <v>257603</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>244</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="5">
-        <v>259803</v>
+        <v>253772</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>245</v>
@@ -5699,21 +5774,21 @@
         <v>10</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="5">
-        <v>263416</v>
+        <v>259803</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>246</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5727,7 +5802,7 @@
         <v>13</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5741,7 +5816,7 @@
         <v>10</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5755,7 +5830,7 @@
         <v>5</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5769,7 +5844,7 @@
         <v>13</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5783,7 +5858,7 @@
         <v>8</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5797,7 +5872,7 @@
         <v>8</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5811,7 +5886,7 @@
         <v>8</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5825,7 +5900,7 @@
         <v>5</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5839,7 +5914,7 @@
         <v>10</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5853,7 +5928,7 @@
         <v>5</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5867,7 +5942,7 @@
         <v>8</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5881,7 +5956,7 @@
         <v>5</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5895,7 +5970,7 @@
         <v>8</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5909,7 +5984,7 @@
         <v>13</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5923,7 +5998,7 @@
         <v>8</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5937,54 +6012,54 @@
         <v>8</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="5">
-        <v>270784</v>
-      </c>
-      <c r="B247" s="6" t="s">
+      <c r="A247" s="9">
+        <v>273291</v>
+      </c>
+      <c r="B247" s="10" t="s">
         <v>263</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="5">
-        <v>271943</v>
+        <v>279511</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C248" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="5">
-        <v>247695</v>
+        <v>270784</v>
       </c>
       <c r="B249" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C249" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D249" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="C249" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D249" s="6" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="5">
-        <v>253781</v>
+        <v>271943</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>267</v>
@@ -5993,12 +6068,12 @@
         <v>10</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="5">
-        <v>211631</v>
+        <v>247695</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>268</v>
@@ -6007,68 +6082,68 @@
         <v>5</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="252" spans="1:4">
-      <c r="A252" s="6">
-        <v>278079</v>
+      <c r="A252" s="5">
+        <v>253781</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>269</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="5">
-        <v>273293</v>
+        <v>211631</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>270</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="254" spans="1:4">
-      <c r="A254" s="5">
-        <v>269965</v>
+      <c r="A254" s="6">
+        <v>278079</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>271</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="5">
-        <v>258464</v>
+        <v>273293</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>272</v>
       </c>
       <c r="C255" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="5">
-        <v>259796</v>
+        <v>269965</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>273</v>
@@ -6077,217 +6152,217 @@
         <v>8</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="257" spans="1:4">
-      <c r="A257" s="6">
-        <v>276388</v>
+      <c r="A257" s="5">
+        <v>258464</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>274</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="5">
-        <v>258455</v>
+        <v>259796</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>275</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="259" spans="1:4">
-      <c r="A259" s="5">
-        <v>279511</v>
+      <c r="A259" s="6">
+        <v>276388</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>276</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="5">
-        <v>246412</v>
+        <v>258455</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>277</v>
       </c>
       <c r="C260" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="261" spans="1:4">
-      <c r="A261" s="6">
-        <v>278647</v>
+      <c r="A261" s="5">
+        <v>246412</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>278</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="262" spans="1:4">
-      <c r="A262" s="5">
-        <v>265803</v>
+      <c r="A262" s="6">
+        <v>278647</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>279</v>
       </c>
       <c r="C262" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="5">
-        <v>259798</v>
+        <v>265803</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>280</v>
       </c>
       <c r="C263" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="5">
-        <v>261757</v>
+        <v>259798</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>281</v>
       </c>
       <c r="C264" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="265" spans="1:4">
-      <c r="A265" s="9">
+      <c r="A265" s="5">
+        <v>261757</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C265" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D265" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
+      <c r="A266" s="9">
         <v>257611</v>
       </c>
-      <c r="B265" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C265" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D265" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4">
-      <c r="A266" s="5">
+      <c r="B266" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="C266" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D266" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
+      <c r="A267" s="5">
         <v>279512</v>
-      </c>
-      <c r="B266" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C266" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D266" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4">
-      <c r="A267" s="6">
-        <v>273152</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>284</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="6">
-        <v>284046</v>
+        <v>273152</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>285</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="269" spans="1:4">
-      <c r="A269" s="8">
+      <c r="A269" s="6">
+        <v>284046</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C269" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D269" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
+      <c r="A270" s="8">
         <v>236219</v>
       </c>
-      <c r="B269" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="C269" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D269" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
-      <c r="A270" s="6">
+      <c r="B270" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C270" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D270" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
+      <c r="A271" s="6">
         <v>277539</v>
       </c>
-      <c r="B270" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C270" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D270" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4">
-      <c r="A271" s="9">
-        <v>273291</v>
-      </c>
-      <c r="B271" s="10" t="s">
+      <c r="B271" s="6" t="s">
         <v>288</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -6301,7 +6376,7 @@
         <v>5</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -6315,7 +6390,7 @@
         <v>5</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -6329,7 +6404,7 @@
         <v>5</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -6343,7 +6418,7 @@
         <v>5</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -6357,7 +6432,7 @@
         <v>5</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -6371,7 +6446,7 @@
         <v>8</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -6385,7 +6460,7 @@
         <v>10</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -6399,7 +6474,7 @@
         <v>13</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -6413,7 +6488,7 @@
         <v>8</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -6427,7 +6502,7 @@
         <v>8</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -6441,7 +6516,7 @@
         <v>8</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -6455,7 +6530,7 @@
         <v>10</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -6469,7 +6544,7 @@
         <v>5</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -6483,7 +6558,7 @@
         <v>10</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -6497,7 +6572,7 @@
         <v>8</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -6511,7 +6586,7 @@
         <v>8</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -6525,7 +6600,7 @@
         <v>8</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -6539,7 +6614,7 @@
         <v>13</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -6553,35 +6628,35 @@
         <v>10</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="291" spans="1:4">
-      <c r="A291" s="5">
-        <v>213858</v>
-      </c>
-      <c r="B291" s="6" t="s">
+      <c r="A291" s="8">
+        <v>275099</v>
+      </c>
+      <c r="B291" s="8" t="s">
         <v>308</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D291" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="9">
+        <v>273295</v>
+      </c>
+      <c r="B292" s="10" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="292" spans="1:4">
-      <c r="A292" s="5">
-        <v>268097</v>
-      </c>
-      <c r="B292" s="6" t="s">
-        <v>310</v>
-      </c>
       <c r="C292" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -6589,158 +6664,158 @@
         <v>276385</v>
       </c>
       <c r="B293" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="9">
+        <v>282669</v>
+      </c>
+      <c r="B294" s="9" t="s">
         <v>311</v>
       </c>
-      <c r="C293" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D293" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4">
-      <c r="A294" s="6">
-        <v>281970</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>312</v>
-      </c>
       <c r="C294" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" s="5">
-        <v>263409</v>
+        <v>280956</v>
       </c>
       <c r="B295" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="5">
+        <v>213858</v>
+      </c>
+      <c r="B296" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="C295" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D295" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4">
-      <c r="A296" s="6">
-        <v>210531</v>
-      </c>
-      <c r="B296" s="6" t="s">
+      <c r="C296" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D296" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C296" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D296" s="6" t="s">
-        <v>309</v>
-      </c>
     </row>
     <row r="297" spans="1:4">
-      <c r="A297" s="6">
-        <v>276019</v>
+      <c r="A297" s="5">
+        <v>268097</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>315</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="298" spans="1:4">
-      <c r="A298" s="9">
-        <v>272827</v>
-      </c>
-      <c r="B298" s="9" t="s">
+      <c r="A298" s="6">
+        <v>281970</v>
+      </c>
+      <c r="B298" s="6" t="s">
         <v>316</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="299" spans="1:4">
       <c r="A299" s="5">
-        <v>279043</v>
+        <v>263409</v>
       </c>
       <c r="B299" s="6" t="s">
         <v>317</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="300" spans="1:4">
-      <c r="A300" s="5">
-        <v>246465</v>
+      <c r="A300" s="6">
+        <v>210531</v>
       </c>
       <c r="B300" s="6" t="s">
         <v>318</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="301" spans="1:4">
       <c r="A301" s="6">
-        <v>261778</v>
+        <v>276019</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>319</v>
       </c>
       <c r="C301" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="302" spans="1:4">
-      <c r="A302" s="5">
-        <v>289953</v>
-      </c>
-      <c r="B302" s="6" t="s">
+      <c r="A302" s="9">
+        <v>272827</v>
+      </c>
+      <c r="B302" s="9" t="s">
         <v>320</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="303" spans="1:4">
-      <c r="A303" s="9">
-        <v>284122</v>
-      </c>
-      <c r="B303" s="9" t="s">
+      <c r="A303" s="5">
+        <v>279043</v>
+      </c>
+      <c r="B303" s="6" t="s">
         <v>321</v>
       </c>
       <c r="C303" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="304" spans="1:4">
-      <c r="A304" s="6">
-        <v>264064</v>
+      <c r="A304" s="5">
+        <v>246465</v>
       </c>
       <c r="B304" s="6" t="s">
         <v>322</v>
@@ -6749,119 +6824,119 @@
         <v>10</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="305" spans="1:4">
-      <c r="A305" s="8">
-        <v>275099</v>
-      </c>
-      <c r="B305" s="8" t="s">
+      <c r="A305" s="6">
+        <v>261778</v>
+      </c>
+      <c r="B305" s="6" t="s">
         <v>323</v>
       </c>
       <c r="C305" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="306" spans="1:4">
-      <c r="A306" s="8">
-        <v>282654</v>
-      </c>
-      <c r="B306" s="8" t="s">
+      <c r="A306" s="5">
+        <v>289953</v>
+      </c>
+      <c r="B306" s="6" t="s">
         <v>324</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="307" spans="1:4">
       <c r="A307" s="9">
-        <v>282669</v>
+        <v>284122</v>
       </c>
       <c r="B307" s="9" t="s">
         <v>325</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="308" spans="1:4">
-      <c r="A308" s="9">
+      <c r="A308" s="6">
+        <v>264064</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
+      <c r="A309" s="8">
+        <v>282654</v>
+      </c>
+      <c r="B309" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D309" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
+      <c r="A310" s="9">
         <v>282149</v>
       </c>
-      <c r="B308" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="C308" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D308" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4">
-      <c r="A309" s="5">
-        <v>280956</v>
-      </c>
-      <c r="B309" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C309" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D309" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4">
-      <c r="A310" s="5">
+      <c r="B310" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D310" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
+      <c r="A311" s="5">
         <v>291328</v>
       </c>
-      <c r="B310" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C310" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D310" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4">
-      <c r="A311" s="9">
-        <v>275109</v>
-      </c>
-      <c r="B311" s="9" t="s">
+      <c r="B311" s="6" t="s">
         <v>329</v>
       </c>
       <c r="C311" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D311" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="312" spans="1:4">
       <c r="A312" s="9">
-        <v>273295</v>
-      </c>
-      <c r="B312" s="10" t="s">
+        <v>275109</v>
+      </c>
+      <c r="B312" s="9" t="s">
         <v>330</v>
       </c>
       <c r="C312" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D312" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -6875,7 +6950,7 @@
         <v>13</v>
       </c>
       <c r="D313" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -6889,7 +6964,7 @@
         <v>13</v>
       </c>
       <c r="D314" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6903,7 +6978,7 @@
         <v>8</v>
       </c>
       <c r="D315" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6917,7 +6992,7 @@
         <v>13</v>
       </c>
       <c r="D316" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6931,7 +7006,7 @@
         <v>13</v>
       </c>
       <c r="D317" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6945,7 +7020,7 @@
         <v>8</v>
       </c>
       <c r="D318" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6959,7 +7034,7 @@
         <v>5</v>
       </c>
       <c r="D319" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6973,7 +7048,7 @@
         <v>10</v>
       </c>
       <c r="D320" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6987,7 +7062,7 @@
         <v>13</v>
       </c>
       <c r="D321" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -7001,7 +7076,7 @@
         <v>5</v>
       </c>
       <c r="D322" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -7015,7 +7090,7 @@
         <v>10</v>
       </c>
       <c r="D323" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -7029,7 +7104,7 @@
         <v>5</v>
       </c>
       <c r="D324" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -7043,7 +7118,7 @@
         <v>5</v>
       </c>
       <c r="D325" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -7057,7 +7132,7 @@
         <v>5</v>
       </c>
       <c r="D326" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -7071,7 +7146,7 @@
         <v>13</v>
       </c>
       <c r="D327" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -7085,7 +7160,7 @@
         <v>13</v>
       </c>
       <c r="D328" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -7099,7 +7174,7 @@
         <v>5</v>
       </c>
       <c r="D329" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -7113,7 +7188,7 @@
         <v>10</v>
       </c>
       <c r="D330" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -7127,7 +7202,7 @@
         <v>13</v>
       </c>
       <c r="D331" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -7141,7 +7216,7 @@
         <v>8</v>
       </c>
       <c r="D332" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -7155,7 +7230,7 @@
         <v>5</v>
       </c>
       <c r="D333" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -7169,7 +7244,7 @@
         <v>13</v>
       </c>
       <c r="D334" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -7183,7 +7258,7 @@
         <v>8</v>
       </c>
       <c r="D335" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -7197,7 +7272,7 @@
         <v>8</v>
       </c>
       <c r="D336" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -7211,7 +7286,7 @@
         <v>5</v>
       </c>
       <c r="D337" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -7225,7 +7300,7 @@
         <v>13</v>
       </c>
       <c r="D338" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -7239,7 +7314,7 @@
         <v>10</v>
       </c>
       <c r="D339" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -7253,7 +7328,7 @@
         <v>8</v>
       </c>
       <c r="D340" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -7267,7 +7342,7 @@
         <v>13</v>
       </c>
       <c r="D341" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -7281,7 +7356,7 @@
         <v>5</v>
       </c>
       <c r="D342" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -7295,7 +7370,7 @@
         <v>10</v>
       </c>
       <c r="D343" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -7309,7 +7384,7 @@
         <v>5</v>
       </c>
       <c r="D344" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -7323,7 +7398,7 @@
         <v>10</v>
       </c>
       <c r="D345" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -7337,7 +7412,7 @@
         <v>10</v>
       </c>
       <c r="D346" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -7351,7 +7426,7 @@
         <v>13</v>
       </c>
       <c r="D347" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -7365,7 +7440,7 @@
         <v>5</v>
       </c>
       <c r="D348" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -7379,7 +7454,7 @@
         <v>8</v>
       </c>
       <c r="D349" s="6" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -7928,8 +8003,344 @@
         <v>395</v>
       </c>
     </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="B389" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="C389" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D389" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4">
+      <c r="A390" s="9">
+        <v>308642</v>
+      </c>
+      <c r="B390" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="C390" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D390" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4">
+      <c r="A391" s="9">
+        <v>249878</v>
+      </c>
+      <c r="B391" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="C391" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D391" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4">
+      <c r="A392" s="9">
+        <v>292239</v>
+      </c>
+      <c r="B392" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C392" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D392" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4">
+      <c r="A393" s="9">
+        <v>294618</v>
+      </c>
+      <c r="B393" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="C393" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4">
+      <c r="A394" s="9">
+        <v>294620</v>
+      </c>
+      <c r="B394" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C394" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D394" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4">
+      <c r="A395" s="9">
+        <v>302685</v>
+      </c>
+      <c r="B395" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="C395" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D395" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4">
+      <c r="A396" s="9">
+        <v>207160</v>
+      </c>
+      <c r="B396" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="C396" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D396" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4">
+      <c r="A397" s="9">
+        <v>181642</v>
+      </c>
+      <c r="B397" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C397" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D397" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4">
+      <c r="A398" s="9">
+        <v>181737</v>
+      </c>
+      <c r="B398" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="C398" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D398" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4">
+      <c r="A399" s="9">
+        <v>205160</v>
+      </c>
+      <c r="B399" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="C399" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D399" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4">
+      <c r="A400" s="9">
+        <v>212794</v>
+      </c>
+      <c r="B400" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="C400" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D400" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
+      <c r="A401" s="9">
+        <v>209640</v>
+      </c>
+      <c r="B401" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="C401" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D401" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4">
+      <c r="A402" s="9">
+        <v>302253</v>
+      </c>
+      <c r="B402" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C402" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D402" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4">
+      <c r="A403" s="9">
+        <v>304230</v>
+      </c>
+      <c r="B403" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="C403" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D403" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
+      <c r="A404" s="9">
+        <v>228868</v>
+      </c>
+      <c r="B404" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C404" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D404" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4">
+      <c r="A405" s="9">
+        <v>283746</v>
+      </c>
+      <c r="B405" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="C405" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D405" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
+      <c r="A406" s="9">
+        <v>287546</v>
+      </c>
+      <c r="B406" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="C406" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D406" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
+      <c r="A407" s="9">
+        <v>289564</v>
+      </c>
+      <c r="B407" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="C407" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D407" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
+      <c r="A408" s="9">
+        <v>289949</v>
+      </c>
+      <c r="B408" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C408" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D408" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
+      <c r="A409" s="9">
+        <v>294884</v>
+      </c>
+      <c r="B409" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="C409" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D409" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4">
+      <c r="A410" s="9">
+        <v>257631</v>
+      </c>
+      <c r="B410" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="C410" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D410" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4">
+      <c r="A411" s="9">
+        <v>275241</v>
+      </c>
+      <c r="B411" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C411" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D411" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
+      <c r="A412" s="9">
+        <v>305448</v>
+      </c>
+      <c r="B412" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="C412" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D412" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B32 B44 B98 B310 B39:B40 B49 B46:B47 B36:B37 B165 B279 B167:B168 B188:B194 B299:B300 B89 B148:B153 B100:B101 B110:B138 B171 B350:B351 B297 B293:B294 B291 B323 B266:B268 B247:B254 B326:B327 B282:B284 B108 B78:B83 B231:B234 B304:B307 B218:B228 B341 B389:B1048576 B160:B163 B180 B156:B157 B85:B86 B106 B286:B287 B216 B337:B338 B214 B53:B75 B51 B317:B320 B203 B332 B272 B243:B245 B236:B238 B329:B330 B208:B211 B141:B143 B315 B174:B175">
+  <conditionalFormatting sqref="B1:B32 B44 B98 B175:B176 B39:B40 B49 B46:B47 B36:B37 B165 B279 B167:B168 B188:B194 B291 B243:B245 B89 B148:B153 B100:B101 B110:B138 B171 B350:B351 B315 B141:B143 B208:B211 B323 B220:B229 B267:B269 B326:B327 B282:B284 B108 B78:B83 B231:B234 B329:B330 B272 B236:B238 B218 B413:B1048576 B341 B308:B309 B301 B160:B163 B180 B156:B157 B85:B86 B106 B286:B287 B216 B337:B338 B214 B53:B75 B51 B317:B320 B203 B332 B311 B293:B294 B298 B303:B304 B296 B249:B256">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
